--- a/testDLM.xlsx
+++ b/testDLM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antoine\Source\Repos\CompFinance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bernardo\dev\repos\CompFinance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83F81EB-3DBF-4DAF-B4A2-0847A936B429}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4581E5D5-4A14-4B71-A1F8-94B2AA783AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="44092" windowHeight="24292" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17769" yWindow="6146" windowWidth="17280" windowHeight="10071" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,15 +19,10 @@
     <sheet name="Sheet1 (4)" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -188,8 +183,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -329,7 +324,7 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -338,29 +333,28 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="6" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="6" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="5"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -694,67 +688,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:AA61"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3046875" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3046875" style="8"/>
-    <col min="16" max="16" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="8"/>
+    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.45">
       <c r="T3" t="str">
         <f>_xll.xPutMultiStats(D4:F4,1,2,"stats")</f>
         <v>stats</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>0.01</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.25</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -764,75 +758,75 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.5</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -854,8 +848,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.8</v>
       </c>
       <c r="E12" s="2">
@@ -872,11 +866,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.5</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.7</v>
       </c>
       <c r="F13" s="2">
@@ -889,7 +883,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -900,7 +894,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -924,7 +918,7 @@
         <v>google 0.50 0.50</v>
       </c>
       <c r="U16" s="9">
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V16" t="e">
         <v>#N/A</v>
@@ -935,7 +929,7 @@
       </c>
       <c r="Y16" s="9"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -953,7 +947,7 @@
         <v>amazon 0.50 0.50</v>
       </c>
       <c r="U17" s="9">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="V17" t="e">
         <v>#N/A</v>
@@ -964,7 +958,7 @@
       </c>
       <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C18" s="3" t="str">
         <f t="array" ref="C18:H30">_xll.xViewDLM(D16)</f>
         <v/>
@@ -995,7 +989,7 @@
         <v>starbucks 0.50 0.50</v>
       </c>
       <c r="U18" s="9">
-        <v>22.612857494939018</v>
+        <v>25.15689747080819</v>
       </c>
       <c r="V18" t="e">
         <v>#N/A</v>
@@ -1006,7 +1000,7 @@
       </c>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="str">
         <v>google</v>
       </c>
@@ -1014,7 +1008,7 @@
         <v>subnormal</v>
       </c>
       <c r="E19" s="5">
-        <v>66.666666666666671</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="F19" s="5">
         <v>0.60000000000000009</v>
@@ -1043,7 +1037,7 @@
       </c>
       <c r="Y19" s="9"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C20" t="str">
         <v>amazon</v>
       </c>
@@ -1072,7 +1066,7 @@
         <v>amazon google 0.50 0.50</v>
       </c>
       <c r="U20" s="9">
-        <v>4819.5123831342207</v>
+        <v>5125.4357589745241</v>
       </c>
       <c r="V20" t="e">
         <v>#N/A</v>
@@ -1080,7 +1074,7 @@
       <c r="Y20" s="9"/>
       <c r="AA20" s="7"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C21" t="str">
         <v>starbucks</v>
       </c>
@@ -1088,7 +1082,7 @@
         <v>subnormal</v>
       </c>
       <c r="E21" s="7">
-        <v>33.333333333333329</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="F21" s="7">
         <v>0.75</v>
@@ -1109,14 +1103,14 @@
         <v>amazon amazon 0.50 0.50</v>
       </c>
       <c r="U21" s="9">
-        <v>9224.8911323503617</v>
+        <v>10264.249148007915</v>
       </c>
       <c r="V21" t="e">
         <v>#N/A</v>
       </c>
       <c r="Y21" s="9"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C22" t="e">
         <v>#N/A</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>starbucks google 0.50 0.50</v>
       </c>
       <c r="U22" s="9">
-        <v>1140.3114289264086</v>
+        <v>1284.4065790705861</v>
       </c>
       <c r="V22" t="e">
         <v>#N/A</v>
@@ -1153,7 +1147,7 @@
       <c r="Y22" s="9"/>
       <c r="AA22" s="7"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C23" t="e">
         <v>#N/A</v>
       </c>
@@ -1182,7 +1176,7 @@
         <v>starbucks amazon 0.50 0.50</v>
       </c>
       <c r="U23" s="9">
-        <v>2153.0412675187622</v>
+        <v>2570.0939319577446</v>
       </c>
       <c r="V23" t="e">
         <v>#N/A</v>
@@ -1190,7 +1184,7 @@
       <c r="Y23" s="9"/>
       <c r="AA23" s="7"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C24" t="e">
         <v>#N/A</v>
       </c>
@@ -1219,14 +1213,14 @@
         <v>starbucks starbucks 0.50 0.50</v>
       </c>
       <c r="U24" s="9">
-        <v>548.65903254552404</v>
+        <v>654.56114640888813</v>
       </c>
       <c r="V24" t="e">
         <v>#N/A</v>
       </c>
       <c r="Y24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C25" t="e">
         <v>#N/A</v>
       </c>
@@ -1251,13 +1245,13 @@
         <v>google 1.00 1.00</v>
       </c>
       <c r="U25">
-        <v>46.462565020808249</v>
+        <v>50.50277782726215</v>
       </c>
       <c r="V25" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C26" t="e">
         <v>#N/A</v>
       </c>
@@ -1282,13 +1276,13 @@
         <v>amazon 1.00 1.00</v>
       </c>
       <c r="U26">
-        <v>95.954601969190364</v>
+        <v>101.51114758705609</v>
       </c>
       <c r="V26" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C27" t="e">
         <v>#N/A</v>
       </c>
@@ -1313,13 +1307,13 @@
         <v>starbucks 1.00 1.00</v>
       </c>
       <c r="U27">
-        <v>22.72662860436218</v>
+        <v>25.315872776551071</v>
       </c>
       <c r="V27" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C28" t="e">
         <v>#N/A</v>
       </c>
@@ -1344,13 +1338,13 @@
         <v>google google 1.00 1.00</v>
       </c>
       <c r="U28">
-        <v>2293.5689471641099</v>
+        <v>2666.2210548991438</v>
       </c>
       <c r="V28" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C29" t="e">
         <v>#N/A</v>
       </c>
@@ -1375,13 +1369,13 @@
         <v>amazon google 1.00 1.00</v>
       </c>
       <c r="U29">
-        <v>4505.2650985858845</v>
+        <v>5250.8423879233615</v>
       </c>
       <c r="V29" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C30" t="e">
         <v>#N/A</v>
       </c>
@@ -1406,17 +1400,17 @@
         <v>amazon amazon 1.00 1.00</v>
       </c>
       <c r="U30">
-        <v>9427.265093697164</v>
+        <v>10533.19615862805</v>
       </c>
       <c r="V30" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>19</v>
       </c>
@@ -1438,7 +1432,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33">
         <f t="array" ref="B33:B35">TRANSPOSE(D8:F8)</f>
         <v>50</v>
@@ -1453,19 +1447,19 @@
       </c>
       <c r="E33" s="7">
         <f>IF(F19=0,E19/D33,E19)</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="F33" s="11">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="F33" s="7">
         <f>IF(D19="subnormal",E33-B33,E33+B33)</f>
-        <v>16.666666666666671</v>
+        <v>16.666666666666657</v>
       </c>
       <c r="G33" s="7">
         <f>F33^2*(EXP(D33^2)-1)</f>
-        <v>120.36928182231684</v>
+        <v>120.36928182231664</v>
       </c>
       <c r="H33" s="7">
         <f>SQRT(G33)</f>
-        <v>10.971293534598226</v>
+        <v>10.971293534598217</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -1473,7 +1467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>100</v>
       </c>
@@ -1489,7 +1483,7 @@
         <f>IF(F20=0,E20/D34,E20)</f>
         <v>200.00000000000006</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="7">
         <f>IF(D20="subnormal",E34-B34,E34+B34)</f>
         <v>300.00000000000006</v>
       </c>
@@ -1524,14 +1518,14 @@
       </c>
       <c r="P34" s="10">
         <f>N34*F33*F34*(EXP(N34*L34*D33*D34)-1)</f>
-        <v>125.88810517129463</v>
+        <v>125.88810517129451</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R34" s="10">
         <f>W49</f>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="V34" t="str">
         <f t="array" ref="V34:V36">TRANSPOSE(D4:F4)</f>
@@ -1539,10 +1533,10 @@
       </c>
       <c r="W34" s="9">
         <f>U16</f>
-        <v>50.250643505236695</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.4">
+        <v>50.250643505236702</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>25</v>
       </c>
@@ -1556,19 +1550,19 @@
       </c>
       <c r="E35" s="7">
         <f>IF(F21=0,E21/D35,E21)</f>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="F35" s="11">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="F35" s="7">
         <f>IF(D21="subnormal",E35-B35,E35+B35)</f>
-        <v>8.3333333333333286</v>
+        <v>8.3333333333333357</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>52.434351177798455</v>
+        <v>52.43435117779854</v>
       </c>
       <c r="H35" s="7">
         <f>SQRT(G35)</f>
-        <v>7.241156756886185</v>
+        <v>7.2411567568861912</v>
       </c>
       <c r="J35" s="6" t="str">
         <f>C34&amp;"/"&amp;C35</f>
@@ -1593,24 +1587,24 @@
       </c>
       <c r="P35" s="10">
         <f>N35*F34*F35*(EXP(N35*L35*D34*D35)-1)</f>
-        <v>71.610617912915259</v>
+        <v>71.61061791291533</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R35" s="10">
         <f>Y49</f>
-        <v>-5.947162173990364</v>
+        <v>35.467226277137343</v>
       </c>
       <c r="V35" t="str">
         <v>amazon</v>
       </c>
       <c r="W35" s="9">
         <f>U17</f>
-        <v>95.476143613249917</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.4">
+        <v>100.75275413519344</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J36" s="6" t="s">
         <v>26</v>
       </c>
@@ -1640,28 +1634,28 @@
       </c>
       <c r="R36" s="10">
         <f>W50</f>
-        <v>4.0007883135083375</v>
+        <v>20.256292567212995</v>
       </c>
       <c r="V36" t="str">
         <v>starbucks</v>
       </c>
       <c r="W36" s="9">
         <f>U18</f>
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="W38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1673,16 +1667,16 @@
       <c r="K39" s="6"/>
       <c r="W39" s="7">
         <f t="array" ref="W39:Y39">TRANSPOSE(U41:U43)</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X39" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="Y39" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -1703,7 +1697,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1715,7 +1709,7 @@
       <c r="K41" s="6"/>
       <c r="U41" s="7">
         <f t="array" ref="U41:U43">W34:W36</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V41" t="str">
         <f t="array" ref="V41:V43">V34:V36</f>
@@ -1727,14 +1721,14 @@
       </c>
       <c r="X41" s="9">
         <f>W42</f>
-        <v>4819.5123831342207</v>
+        <v>5125.4357589745241</v>
       </c>
       <c r="Y41" s="9">
         <f>W43</f>
-        <v>1140.3114289264086</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.4">
+        <v>1284.4065790705861</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -1745,25 +1739,25 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="U42" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="V42" t="str">
         <v>amazon</v>
       </c>
       <c r="W42" s="9">
         <f>U20</f>
-        <v>4819.5123831342207</v>
+        <v>5125.4357589745241</v>
       </c>
       <c r="X42" s="9">
         <f>U21</f>
-        <v>9224.8911323503617</v>
+        <v>10264.249148007915</v>
       </c>
       <c r="Y42" s="9">
         <f>X43</f>
-        <v>2153.0412675187622</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.4">
+        <v>2570.0939319577446</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -1774,25 +1768,25 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="U43" s="7">
-        <v>22.612857494939018</v>
+        <v>25.15689747080819</v>
       </c>
       <c r="V43" t="str">
         <v>starbucks</v>
       </c>
       <c r="W43" s="9">
         <f>U22</f>
-        <v>1140.3114289264086</v>
+        <v>1284.4065790705861</v>
       </c>
       <c r="X43" s="9">
         <f>U23</f>
-        <v>2153.0412675187622</v>
+        <v>2570.0939319577446</v>
       </c>
       <c r="Y43" s="9">
         <f>U24</f>
-        <v>548.65903254552404</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.4">
+        <v>654.56114640888813</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -1803,7 +1797,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -1817,7 +1811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -1829,16 +1823,16 @@
       <c r="K46" s="6"/>
       <c r="W46" s="7">
         <f t="array" ref="W46:Y46">W39:Y39</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X46" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="Y46" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -1859,7 +1853,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -1871,7 +1865,7 @@
       <c r="K48" s="6"/>
       <c r="U48" s="7">
         <f t="array" ref="U48:U50">U41:U43</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V48" t="str">
         <f t="array" ref="V48:V50">V41:V43</f>
@@ -1879,18 +1873,18 @@
       </c>
       <c r="W48" s="9">
         <f>W41-$U48*W$46</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="X48" s="9">
         <f t="shared" ref="X48:Y48" si="1">X41-$U48*X$46</f>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.4">
+        <v>20.256292567212995</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -1901,25 +1895,25 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
       <c r="U49" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="V49" t="str">
         <v>amazon</v>
       </c>
       <c r="W49" s="9">
         <f t="shared" ref="W49:Y49" si="2">W42-$U49*W$46</f>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="X49" s="9">
         <f t="shared" si="2"/>
-        <v>109.19713309243889</v>
+        <v>113.13168218117607</v>
       </c>
       <c r="Y49" s="9">
         <f t="shared" si="2"/>
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.4">
+        <v>35.467226277137343</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -1930,25 +1924,25 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
       <c r="U50" s="7">
-        <v>22.612857494939018</v>
+        <v>25.15689747080819</v>
       </c>
       <c r="V50" t="str">
         <v>starbucks</v>
       </c>
       <c r="W50" s="9">
         <f t="shared" ref="W50:Y50" si="3">W43-$U50*W$46</f>
-        <v>4.0007883135083375</v>
+        <v>20.256292567212995</v>
       </c>
       <c r="X50" s="9">
         <f t="shared" si="3"/>
-        <v>-5.947162173990364</v>
+        <v>35.467226277137343</v>
       </c>
       <c r="Y50" s="9">
         <f t="shared" si="3"/>
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.4">
+        <v>21.691656052132657</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -1959,7 +1953,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -1973,7 +1967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -1985,18 +1979,18 @@
       <c r="K53" s="6"/>
       <c r="W53" s="7">
         <f>SQRT(W48)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="X53" s="7">
         <f>SQRT(X49)</f>
-        <v>10.449743207009391</v>
+        <v>10.636337818120298</v>
       </c>
       <c r="Y53" s="7">
         <f>SQRT(Y50)</f>
-        <v>6.1088221826391642</v>
-      </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.4">
+        <v>4.6574301983102933</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -2017,7 +2011,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -2029,11 +2023,11 @@
       <c r="K55" s="6"/>
       <c r="T55" s="10">
         <f>U55/W34</f>
-        <v>0.14506581646941213</v>
+        <v>0.1450658164694115</v>
       </c>
       <c r="U55" s="7">
         <f t="array" ref="U55:U57">TRANSPOSE(W53:Y53)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="V55" t="str">
         <f t="array" ref="V55:V57">V48:V50</f>
@@ -2045,14 +2039,14 @@
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55:Y55" si="4">X48/$U55/X$53</f>
-        <v>0.28585144347144498</v>
+        <v>0.80666638531931467</v>
       </c>
       <c r="Y55" s="9">
         <f t="shared" si="4"/>
-        <v>8.98424061952042E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.4">
+        <v>0.5966324796294894</v>
+      </c>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -2064,28 +2058,28 @@
       <c r="K56" s="6"/>
       <c r="T56" s="10">
         <f>U56/W35</f>
-        <v>0.10944873568981481</v>
+        <v>0.10556870538594014</v>
       </c>
       <c r="U56" s="7">
-        <v>10.449743207009391</v>
+        <v>10.636337818120298</v>
       </c>
       <c r="V56" t="str">
         <v>amazon</v>
       </c>
       <c r="W56" s="9">
         <f t="shared" ref="W56:Y56" si="5">W49/$U56/W$53</f>
-        <v>0.28585144347144503</v>
+        <v>0.80666638531931467</v>
       </c>
       <c r="X56" s="9">
         <f t="shared" si="5"/>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Y56" s="9">
         <f t="shared" si="5"/>
-        <v>-9.3163689561357926E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.4">
+        <v>0.71595998212359213</v>
+      </c>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -2097,28 +2091,28 @@
       <c r="K57" s="6"/>
       <c r="T57" s="10">
         <f>U57/W36</f>
-        <v>0.27014817494898108</v>
+        <v>0.18513531741005537</v>
       </c>
       <c r="U57" s="7">
-        <v>6.1088221826391642</v>
+        <v>4.6574301983102933</v>
       </c>
       <c r="V57" t="str">
         <v>starbucks</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:Y57" si="6">W50/$U57/W$53</f>
-        <v>8.9842406195204214E-2</v>
+        <v>0.59663247962948929</v>
       </c>
       <c r="X57" s="9">
         <f t="shared" si="6"/>
-        <v>-9.3163689561357926E-2</v>
+        <v>0.71595998212359202</v>
       </c>
       <c r="Y57" s="9">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -2129,7 +2123,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -2140,7 +2134,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -2151,7 +2145,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -2171,26 +2165,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:AA80"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3046875" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3046875" style="8"/>
-    <col min="16" max="16" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="34.3828125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="8"/>
+    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.45">
       <c r="X2" t="s">
         <v>30</v>
       </c>
@@ -2198,7 +2192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2213,26 +2207,26 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0.01</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>0.01</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>0.01</v>
       </c>
       <c r="T4" t="str">
@@ -2246,22 +2240,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2278,75 +2272,75 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0.05</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0.08</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -2368,8 +2362,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.3</v>
       </c>
       <c r="E12" s="2">
@@ -2386,11 +2380,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>-0.1</v>
       </c>
       <c r="F13" s="2">
@@ -2403,7 +2397,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -2414,7 +2408,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -2444,14 +2438,14 @@
         <v>google 0.50 0.50</v>
       </c>
       <c r="U16" s="9">
-        <v>50.250643505236695</v>
-      </c>
-      <c r="V16" s="20">
+        <v>50.250643505236702</v>
+      </c>
+      <c r="V16" s="19">
         <v>50.00001772886462</v>
       </c>
       <c r="Y16" s="9"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2475,14 +2469,14 @@
         <v>amazon 0.50 0.50</v>
       </c>
       <c r="U17" s="9">
-        <v>95.476143613249917</v>
-      </c>
-      <c r="V17" s="20">
+        <v>100.75275413519344</v>
+      </c>
+      <c r="V17" s="19">
         <v>99.999953429352431</v>
       </c>
       <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C18" s="3" t="str">
         <f t="array" ref="C18:H30">_xll.xViewDLM(D16)</f>
         <v/>
@@ -2519,14 +2513,14 @@
         <v>starbucks 0.50 0.50</v>
       </c>
       <c r="U18" s="9">
-        <v>22.612857494939018</v>
-      </c>
-      <c r="V18" s="20">
+        <v>25.15689747080819</v>
+      </c>
+      <c r="V18" s="19">
         <v>25.000058902133254</v>
       </c>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="str">
         <v>google</v>
       </c>
@@ -2534,7 +2528,7 @@
         <v>subnormal</v>
       </c>
       <c r="E19" s="5">
-        <v>66.666666666666671</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="F19" s="5">
         <v>0.60000000000000009</v>
@@ -2561,16 +2555,16 @@
       <c r="U19" s="9">
         <v>2578.2661789716112</v>
       </c>
-      <c r="V19" s="20">
+      <c r="V19" s="19">
         <v>2554.7757267453712</v>
       </c>
       <c r="W19" s="7">
         <f>U19-U16*U16</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="Y19" s="9"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C20" t="str">
         <v>amazon</v>
       </c>
@@ -2602,19 +2596,19 @@
         <v>amazon google 0.50 0.50</v>
       </c>
       <c r="U20" s="9">
-        <v>4819.5123831342207</v>
-      </c>
-      <c r="V20" s="20">
+        <v>5125.4357589745241</v>
+      </c>
+      <c r="V20" s="19">
         <v>5022.445075340017</v>
       </c>
       <c r="W20" s="7">
         <f>U20-U16*U17</f>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="Y20" s="9"/>
       <c r="AA20" s="7"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C21" t="str">
         <v>starbucks</v>
       </c>
@@ -2622,7 +2616,7 @@
         <v>subnormal</v>
       </c>
       <c r="E21" s="7">
-        <v>33.333333333333329</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="F21" s="7">
         <v>0.75</v>
@@ -2646,18 +2640,18 @@
         <v>amazon amazon 0.50 0.50</v>
       </c>
       <c r="U21" s="9">
-        <v>9224.8911323503617</v>
-      </c>
-      <c r="V21" s="20">
+        <v>10264.249148007915</v>
+      </c>
+      <c r="V21" s="19">
         <v>10112.557083136648</v>
       </c>
       <c r="W21" s="7">
         <f>U21-U17*U17</f>
-        <v>109.19713309243889</v>
+        <v>113.13168218117607</v>
       </c>
       <c r="Y21" s="9"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C22" t="e">
         <v>#N/A</v>
       </c>
@@ -2689,19 +2683,19 @@
         <v>starbucks google 0.50 0.50</v>
       </c>
       <c r="U22" s="9">
-        <v>1140.3114289264086</v>
-      </c>
-      <c r="V22" s="20">
+        <v>1284.4065790705861</v>
+      </c>
+      <c r="V22" s="19">
         <v>1253.1607732194359</v>
       </c>
       <c r="W22" s="7">
         <f>U22-U18*U16</f>
-        <v>4.0007883135083375</v>
+        <v>20.256292567212995</v>
       </c>
       <c r="Y22" s="9"/>
       <c r="AA22" s="7"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C23" t="e">
         <v>#N/A</v>
       </c>
@@ -2733,19 +2727,19 @@
         <v>starbucks amazon 0.50 0.50</v>
       </c>
       <c r="U23" s="9">
-        <v>2153.0412675187622</v>
-      </c>
-      <c r="V23" s="20">
+        <v>2570.0939319577446</v>
+      </c>
+      <c r="V23" s="19">
         <v>2495.3110817065335</v>
       </c>
       <c r="W23" s="7">
         <f>U23-U18*U17</f>
-        <v>-5.947162173990364</v>
+        <v>35.467226277137343</v>
       </c>
       <c r="Y23" s="9"/>
       <c r="AA23" s="7"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C24" t="e">
         <v>#N/A</v>
       </c>
@@ -2777,18 +2771,18 @@
         <v>starbucks starbucks 0.50 0.50</v>
       </c>
       <c r="U24" s="9">
-        <v>548.65903254552404</v>
-      </c>
-      <c r="V24" s="20">
+        <v>654.56114640888813</v>
+      </c>
+      <c r="V24" s="19">
         <v>647.55147391399305</v>
       </c>
       <c r="W24" s="7">
         <f>U24-U18*U18</f>
-        <v>37.317708459104324</v>
+        <v>21.691656052132657</v>
       </c>
       <c r="Y24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C25" t="e">
         <v>#N/A</v>
       </c>
@@ -2825,23 +2819,23 @@
         <v>google 1.00 1.00</v>
       </c>
       <c r="U25" s="7">
-        <v>46.462565020808249</v>
-      </c>
-      <c r="V25" s="21">
+        <v>50.50277782726215</v>
+      </c>
+      <c r="V25" s="20">
         <v>50.000272818845943</v>
       </c>
-      <c r="X25" s="17" t="str">
+      <c r="X25" s="16" t="str">
         <f t="array" ref="X25:Z33">_xll.xValue(D16,T4,U12,,,U13,U11)</f>
         <v>google 1.00 1.00</v>
       </c>
-      <c r="Y25" s="18">
+      <c r="Y25" s="17">
         <v>46.462428396446704</v>
       </c>
-      <c r="Z25" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z25" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C26" t="e">
         <v>#N/A</v>
       </c>
@@ -2877,22 +2871,22 @@
         <v>amazon 1.00 1.00</v>
       </c>
       <c r="U26" s="7">
-        <v>95.954601969190364</v>
-      </c>
-      <c r="V26" s="21">
+        <v>101.51114758705609</v>
+      </c>
+      <c r="V26" s="20">
         <v>99.999834036142801</v>
       </c>
-      <c r="X26" s="17" t="str">
+      <c r="X26" s="16" t="str">
         <v>amazon 1.00 1.00</v>
       </c>
-      <c r="Y26" s="18">
-        <v>95.95469713213491</v>
-      </c>
-      <c r="Z26" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y26" s="17">
+        <v>95.954697132134939</v>
+      </c>
+      <c r="Z26" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C27" t="e">
         <v>#N/A</v>
       </c>
@@ -2928,22 +2922,22 @@
         <v>starbucks 1.00 1.00</v>
       </c>
       <c r="U27" s="7">
-        <v>22.72662860436218</v>
-      </c>
-      <c r="V27" s="21">
+        <v>25.315872776551071</v>
+      </c>
+      <c r="V27" s="20">
         <v>25.000388137689914</v>
       </c>
-      <c r="X27" s="17" t="str">
+      <c r="X27" s="16" t="str">
         <v>starbucks 1.00 1.00</v>
       </c>
-      <c r="Y27" s="18">
-        <v>22.726340449128799</v>
-      </c>
-      <c r="Z27" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y27" s="17">
+        <v>22.726340449128806</v>
+      </c>
+      <c r="Z27" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C28" t="e">
         <v>#N/A</v>
       </c>
@@ -2971,22 +2965,22 @@
         <v>google google 1.00 1.00</v>
       </c>
       <c r="U28" s="7">
-        <v>2293.5689471641099</v>
-      </c>
-      <c r="V28" s="21">
+        <v>2666.2210548991438</v>
+      </c>
+      <c r="V28" s="20">
         <v>2620.2864548711691</v>
       </c>
-      <c r="X28" s="17" t="str">
+      <c r="X28" s="16" t="str">
         <v>google google 1.00 1.00</v>
       </c>
-      <c r="Y28" s="18">
+      <c r="Y28" s="17">
         <v>2335.5669128384684</v>
       </c>
-      <c r="Z28" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z28" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C29" t="e">
         <v>#N/A</v>
       </c>
@@ -3014,22 +3008,22 @@
         <v>amazon google 1.00 1.00</v>
       </c>
       <c r="U29" s="7">
-        <v>4505.2650985858845</v>
-      </c>
-      <c r="V29" s="21">
+        <v>5250.8423879233615</v>
+      </c>
+      <c r="V29" s="20">
         <v>5044.79057984681</v>
       </c>
-      <c r="X29" s="17" t="str">
+      <c r="X29" s="16" t="str">
         <v>amazon google 1.00 1.00</v>
       </c>
-      <c r="Y29" s="18">
-        <v>4511.8491698768121</v>
-      </c>
-      <c r="Z29" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y29" s="17">
+        <v>4511.849169876813</v>
+      </c>
+      <c r="Z29" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C30" t="e">
         <v>#N/A</v>
       </c>
@@ -3057,22 +3051,22 @@
         <v>amazon amazon 1.00 1.00</v>
       </c>
       <c r="U30" s="7">
-        <v>9427.265093697164</v>
-      </c>
-      <c r="V30" s="21">
+        <v>10533.19615862805</v>
+      </c>
+      <c r="V30" s="20">
         <v>10225.23606062171</v>
       </c>
-      <c r="X30" s="17" t="str">
+      <c r="X30" s="16" t="str">
         <v>amazon amazon 1.00 1.00</v>
       </c>
-      <c r="Y30" s="18">
-        <v>9426.5431887968825</v>
-      </c>
-      <c r="Z30" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y30" s="17">
+        <v>9426.5431887968844</v>
+      </c>
+      <c r="Z30" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="S31" s="7">
@@ -3082,22 +3076,22 @@
         <v>starbucks google 1.00 1.00</v>
       </c>
       <c r="U31" s="7">
-        <v>1064.5798956631425</v>
-      </c>
-      <c r="V31" s="21">
+        <v>1321.5237989349148</v>
+      </c>
+      <c r="V31" s="20">
         <v>1256.3880030913922</v>
       </c>
-      <c r="X31" s="17" t="str">
+      <c r="X31" s="16" t="str">
         <v>starbucks google 1.00 1.00</v>
       </c>
-      <c r="Y31" s="18">
+      <c r="Y31" s="17">
         <v>1065.7647819045646</v>
       </c>
-      <c r="Z31" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z31" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>19</v>
       </c>
@@ -3130,22 +3124,22 @@
         <v>starbucks amazon 1.00 1.00</v>
       </c>
       <c r="U32" s="7">
-        <v>2168.798536799241</v>
-      </c>
-      <c r="V32" s="21">
+        <v>2640.0792543950542</v>
+      </c>
+      <c r="V32" s="20">
         <v>2490.6275448812899</v>
       </c>
-      <c r="X32" s="17" t="str">
+      <c r="X32" s="16" t="str">
         <v>starbucks amazon 1.00 1.00</v>
       </c>
-      <c r="Y32" s="18">
-        <v>2168.8987778657665</v>
-      </c>
-      <c r="Z32" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="Y32" s="17">
+        <v>2168.898777865767</v>
+      </c>
+      <c r="Z32" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B33">
         <f t="array" ref="B33:B35">TRANSPOSE(D8:F8)</f>
         <v>50</v>
@@ -3160,19 +3154,19 @@
       </c>
       <c r="E33" s="7">
         <f>IF(F19=0,E19/D33,E19)</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="F33" s="11">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="F33" s="7">
         <f>IF(D19="subnormal",E33-B33,E33+B33)</f>
-        <v>16.666666666666671</v>
+        <v>16.666666666666657</v>
       </c>
       <c r="G33" s="7">
         <f>F33^2*(EXP(D33^2)-1)</f>
-        <v>120.36928182231684</v>
+        <v>120.36928182231664</v>
       </c>
       <c r="H33" s="7">
         <f>SQRT(G33)</f>
-        <v>10.971293534598226</v>
+        <v>10.971293534598217</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -3183,22 +3177,22 @@
         <v>starbucks starbucks 1.00 1.00</v>
       </c>
       <c r="U33" s="7">
-        <v>602.83449581503703</v>
-      </c>
-      <c r="V33" s="21">
+        <v>690.47256754379623</v>
+      </c>
+      <c r="V33" s="20">
         <v>677.36004466031011</v>
       </c>
-      <c r="X33" s="17" t="str">
+      <c r="X33" s="16" t="str">
         <v>starbucks starbucks 1.00 1.00</v>
       </c>
-      <c r="Y33" s="18">
-        <v>601.36234481090435</v>
-      </c>
-      <c r="Z33" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="Y33" s="17">
+        <v>601.36234481090446</v>
+      </c>
+      <c r="Z33" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>100</v>
       </c>
@@ -3214,7 +3208,7 @@
         <f>IF(F20=0,E20/D34,E20)</f>
         <v>200.00000000000006</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="7">
         <f>IF(D20="subnormal",E34-B34,E34+B34)</f>
         <v>300.00000000000006</v>
       </c>
@@ -3249,29 +3243,29 @@
       </c>
       <c r="P34" s="10">
         <f>N34*F33*F34*(EXP(N34*L34*D33*D34*K32)-1)</f>
-        <v>22.449450852147237</v>
+        <v>22.449450852147216</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R34" s="10">
         <f>W72</f>
-        <v>21.774727170018195</v>
-      </c>
-      <c r="S34" s="19">
+        <v>62.545028756155261</v>
+      </c>
+      <c r="S34" s="18">
         <v>-3.9997573158002782</v>
       </c>
       <c r="T34" t="str">
         <v>google 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U34" s="19">
-        <v>-3.7880784844280515</v>
-      </c>
-      <c r="V34" s="21">
+      <c r="U34" s="18">
+        <v>0.25213432202577629</v>
+      </c>
+      <c r="V34" s="20">
         <v>2.5508998007966419E-4</v>
       </c>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>25</v>
       </c>
@@ -3285,19 +3279,19 @@
       </c>
       <c r="E35" s="7">
         <f>IF(F21=0,E21/D35,E21)</f>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="F35" s="11">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="F35" s="7">
         <f>IF(D21="subnormal",E35-B35,E35+B35)</f>
-        <v>8.3333333333333286</v>
+        <v>8.3333333333333357</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>52.434351177798455</v>
+        <v>52.43435117779854</v>
       </c>
       <c r="H35" s="7">
         <f>SQRT(G35)</f>
-        <v>7.241156756886185</v>
+        <v>7.2411567568861912</v>
       </c>
       <c r="J35" s="6" t="str">
         <f>C34&amp;"/"&amp;C35</f>
@@ -3322,29 +3316,29 @@
       </c>
       <c r="P35" s="10">
         <f>N35*F34*F35*(EXP(N35*L35*D34*D35*K32)-1)</f>
-        <v>-4.6918972791198925</v>
+        <v>-4.691897279119897</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R35" s="10">
         <f>Y72</f>
-        <v>-5.947162173990364</v>
-      </c>
-      <c r="S35" s="19">
+        <v>35.467226277137343</v>
+      </c>
+      <c r="S35" s="18">
         <v>-1.1740332356118037E-4</v>
       </c>
       <c r="T35" t="str">
         <v>amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U35" s="19">
-        <v>0.4784583559430402</v>
-      </c>
-      <c r="V35" s="21">
+      <c r="U35" s="18">
+        <v>0.75839345186361418</v>
+      </c>
+      <c r="V35" s="20">
         <v>-1.1939321040121053E-4</v>
       </c>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J36" s="6" t="s">
         <v>26</v>
       </c>
@@ -3374,22 +3368,22 @@
       </c>
       <c r="R36" s="10">
         <f>W73</f>
-        <v>4.0007883135083375</v>
-      </c>
-      <c r="S36" s="19">
+        <v>20.256292567212995</v>
+      </c>
+      <c r="S36" s="18">
         <v>4.2800622399665036E-4</v>
       </c>
       <c r="T36" t="str">
         <v>starbucks 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U36" s="19">
-        <v>0.11377110942236469</v>
-      </c>
-      <c r="V36" s="21">
+      <c r="U36" s="18">
+        <v>0.15897530574127283</v>
+      </c>
+      <c r="V36" s="20">
         <v>3.2923555692051073E-4</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="S37" s="7">
@@ -3399,21 +3393,21 @@
         <v>google google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U37" s="7">
-        <v>104.05245292089364</v>
-      </c>
-      <c r="V37" s="21">
+        <v>62.11321507232811</v>
+      </c>
+      <c r="V37" s="20">
         <v>65.517046672380232</v>
       </c>
       <c r="W37" s="7">
         <f t="array" ref="W37:W42">W19:W24</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="Y37" s="10">
         <f>U37-U34*U34</f>
-        <v>89.702914316706924</v>
-      </c>
-    </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.4">
+        <v>62.049643355984713</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="S38" s="7">
@@ -3423,16 +3417,16 @@
         <v>amazon google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U38" s="7">
-        <v>24.925026370739346</v>
-      </c>
-      <c r="V38" s="21">
+        <v>61.123945053402451</v>
+      </c>
+      <c r="V38" s="20">
         <v>22.337743324818906</v>
       </c>
       <c r="W38" s="7">
-        <v>21.774727170018195</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.4">
+        <v>62.545028756155261</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -3449,16 +3443,16 @@
         <v>amazon amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U39" s="7">
-        <v>109.92012331853519</v>
-      </c>
-      <c r="V39" s="21">
+        <v>114.42763379860757</v>
+      </c>
+      <c r="V39" s="20">
         <v>112.70654695394161</v>
       </c>
       <c r="W39" s="7">
-        <v>109.19713309243889</v>
-      </c>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.4">
+        <v>113.13168218117607</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3475,16 +3469,16 @@
         <v>starbucks google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U40" s="7">
-        <v>4.5089139598671686</v>
-      </c>
-      <c r="V40" s="21">
+        <v>22.611793495707627</v>
+      </c>
+      <c r="V40" s="20">
         <v>3.2172061836399646</v>
       </c>
       <c r="W40" s="7">
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.4">
+        <v>20.256292567212995</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -3501,16 +3495,16 @@
         <v>starbucks amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U41" s="7">
-        <v>-5.8557281459403576</v>
-      </c>
-      <c r="V41" s="21">
+        <v>34.445046413408036</v>
+      </c>
+      <c r="V41" s="20">
         <v>-4.7062732320813385</v>
       </c>
       <c r="W41" s="7">
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.4">
+        <v>35.467226277137343</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -3527,16 +3521,16 @@
         <v>starbucks starbucks 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U42" s="7">
-        <v>48.695231506868787</v>
-      </c>
-      <c r="V42" s="21">
+        <v>27.760593594265071</v>
+      </c>
+      <c r="V42" s="20">
         <v>29.815772011327422</v>
       </c>
       <c r="W42" s="7">
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.4">
+        <v>21.691656052132657</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3553,7 +3547,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3570,7 +3564,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -3587,7 +3581,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -3604,7 +3598,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -3621,7 +3615,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3638,7 +3632,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -3655,7 +3649,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3672,7 +3666,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -3689,7 +3683,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3700,7 +3694,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -3711,7 +3705,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3722,7 +3716,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -3733,7 +3727,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3747,7 +3741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3763,10 +3757,10 @@
       </c>
       <c r="W57" s="9">
         <f>U16</f>
-        <v>50.250643505236695</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.4">
+        <v>50.250643505236702</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3781,10 +3775,10 @@
       </c>
       <c r="W58" s="9">
         <f>U17</f>
-        <v>95.476143613249917</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.4">
+        <v>100.75275413519344</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -3799,10 +3793,10 @@
       </c>
       <c r="W59" s="9">
         <f>U18</f>
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3813,7 +3807,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3827,19 +3821,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.45">
       <c r="W62" s="7">
         <f t="array" ref="W62:Y62">TRANSPOSE(U64:U66)</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X62" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="Y62" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.45">
       <c r="W63" t="str">
         <f t="array" ref="W63:Y63">TRANSPOSE(V64:V66)</f>
         <v>google</v>
@@ -3851,10 +3845,10 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:25" x14ac:dyDescent="0.45">
       <c r="U64" s="7">
         <f t="array" ref="U64:U66">W57:W59</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V64" t="str">
         <f t="array" ref="V64:V66">V57:V59</f>
@@ -3866,71 +3860,71 @@
       </c>
       <c r="X64" s="9">
         <f>W65</f>
-        <v>4819.5123831342207</v>
+        <v>5125.4357589745241</v>
       </c>
       <c r="Y64" s="9">
         <f>W66</f>
-        <v>1140.3114289264086</v>
-      </c>
-    </row>
-    <row r="65" spans="20:25" x14ac:dyDescent="0.4">
+        <v>1284.4065790705861</v>
+      </c>
+    </row>
+    <row r="65" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U65" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="V65" t="str">
         <v>amazon</v>
       </c>
       <c r="W65" s="9">
         <f>U20</f>
-        <v>4819.5123831342207</v>
+        <v>5125.4357589745241</v>
       </c>
       <c r="X65" s="9">
         <f>U21</f>
-        <v>9224.8911323503617</v>
+        <v>10264.249148007915</v>
       </c>
       <c r="Y65" s="9">
         <f>X66</f>
-        <v>2153.0412675187622</v>
-      </c>
-    </row>
-    <row r="66" spans="20:25" x14ac:dyDescent="0.4">
+        <v>2570.0939319577446</v>
+      </c>
+    </row>
+    <row r="66" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U66" s="7">
-        <v>22.612857494939018</v>
+        <v>25.15689747080819</v>
       </c>
       <c r="V66" t="str">
         <v>starbucks</v>
       </c>
       <c r="W66" s="9">
         <f>U22</f>
-        <v>1140.3114289264086</v>
+        <v>1284.4065790705861</v>
       </c>
       <c r="X66" s="9">
         <f>U23</f>
-        <v>2153.0412675187622</v>
+        <v>2570.0939319577446</v>
       </c>
       <c r="Y66" s="9">
         <f>U24</f>
-        <v>548.65903254552404</v>
-      </c>
-    </row>
-    <row r="68" spans="20:25" x14ac:dyDescent="0.4">
+        <v>654.56114640888813</v>
+      </c>
+    </row>
+    <row r="68" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W68" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="69" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W69" s="7">
         <f t="array" ref="W69:Y69">W62:Y62</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X69" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="Y69" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="70" spans="20:25" x14ac:dyDescent="0.4">
+        <v>25.15689747080819</v>
+      </c>
+    </row>
+    <row r="70" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W70" t="str">
         <f t="array" ref="W70:Y70">TRANSPOSE(V71:V73)</f>
         <v>google</v>
@@ -3942,10 +3936,10 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="71" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="71" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U71" s="7">
         <f t="array" ref="U71:U73">U64:U66</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V71" t="str">
         <f t="array" ref="V71:V73">V64:V66</f>
@@ -3953,77 +3947,77 @@
       </c>
       <c r="W71" s="9">
         <f t="shared" ref="W71:Y73" si="1">W64-$U71*W$69</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="X71" s="9">
         <f t="shared" si="1"/>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="Y71" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="72" spans="20:25" x14ac:dyDescent="0.4">
+        <v>20.256292567212995</v>
+      </c>
+    </row>
+    <row r="72" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U72" s="7">
-        <v>95.476143613249917</v>
+        <v>100.75275413519344</v>
       </c>
       <c r="V72" t="str">
         <v>amazon</v>
       </c>
       <c r="W72" s="9">
         <f t="shared" si="1"/>
-        <v>21.774727170018195</v>
+        <v>62.545028756155261</v>
       </c>
       <c r="X72" s="9">
         <f t="shared" si="1"/>
-        <v>109.19713309243889</v>
+        <v>113.13168218117607</v>
       </c>
       <c r="Y72" s="9">
         <f t="shared" si="1"/>
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="73" spans="20:25" x14ac:dyDescent="0.4">
+        <v>35.467226277137343</v>
+      </c>
+    </row>
+    <row r="73" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U73" s="7">
-        <v>22.612857494939018</v>
+        <v>25.15689747080819</v>
       </c>
       <c r="V73" t="str">
         <v>starbucks</v>
       </c>
       <c r="W73" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
+        <v>20.256292567212995</v>
       </c>
       <c r="X73" s="9">
         <f t="shared" si="1"/>
-        <v>-5.947162173990364</v>
+        <v>35.467226277137343</v>
       </c>
       <c r="Y73" s="9">
         <f t="shared" si="1"/>
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="75" spans="20:25" x14ac:dyDescent="0.4">
+        <v>21.691656052132657</v>
+      </c>
+    </row>
+    <row r="75" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W75" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="76" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W76" s="7">
         <f>SQRT(W71)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="X76" s="7">
         <f>SQRT(X72)</f>
-        <v>10.449743207009391</v>
+        <v>10.636337818120298</v>
       </c>
       <c r="Y76" s="7">
         <f>SQRT(Y73)</f>
-        <v>6.1088221826391642</v>
-      </c>
-    </row>
-    <row r="77" spans="20:25" x14ac:dyDescent="0.4">
+        <v>4.6574301983102933</v>
+      </c>
+    </row>
+    <row r="77" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W77" t="str">
         <f t="array" ref="W77:Y77">TRANSPOSE(V78:V80)</f>
         <v>google</v>
@@ -4035,14 +4029,14 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="78" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="78" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T78" s="10">
         <f>U78/W57</f>
-        <v>0.14506581646941213</v>
+        <v>0.1450658164694115</v>
       </c>
       <c r="U78" s="7">
         <f t="array" ref="U78:U80">TRANSPOSE(W76:Y76)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="V78" t="str">
         <f t="array" ref="V78:V80">V71:V73</f>
@@ -4054,55 +4048,55 @@
       </c>
       <c r="X78" s="9">
         <f t="shared" si="2"/>
-        <v>0.28585144347144498</v>
+        <v>0.80666638531931467</v>
       </c>
       <c r="Y78" s="9">
         <f t="shared" si="2"/>
-        <v>8.98424061952042E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="20:25" x14ac:dyDescent="0.4">
+        <v>0.5966324796294894</v>
+      </c>
+    </row>
+    <row r="79" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T79" s="10">
         <f>U79/W58</f>
-        <v>0.10944873568981481</v>
+        <v>0.10556870538594014</v>
       </c>
       <c r="U79" s="7">
-        <v>10.449743207009391</v>
+        <v>10.636337818120298</v>
       </c>
       <c r="V79" t="str">
         <v>amazon</v>
       </c>
       <c r="W79" s="9">
         <f t="shared" si="2"/>
-        <v>0.28585144347144503</v>
+        <v>0.80666638531931467</v>
       </c>
       <c r="X79" s="9">
         <f t="shared" si="2"/>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Y79" s="9">
         <f t="shared" si="2"/>
-        <v>-9.3163689561357926E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="20:25" x14ac:dyDescent="0.4">
+        <v>0.71595998212359213</v>
+      </c>
+    </row>
+    <row r="80" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T80" s="10">
         <f>U80/W59</f>
-        <v>0.27014817494898108</v>
+        <v>0.18513531741005537</v>
       </c>
       <c r="U80" s="7">
-        <v>6.1088221826391642</v>
+        <v>4.6574301983102933</v>
       </c>
       <c r="V80" t="str">
         <v>starbucks</v>
       </c>
       <c r="W80" s="9">
         <f t="shared" si="2"/>
-        <v>8.9842406195204214E-2</v>
+        <v>0.59663247962948929</v>
       </c>
       <c r="X80" s="9">
         <f t="shared" si="2"/>
-        <v>-9.3163689561357926E-2</v>
+        <v>0.71595998212359202</v>
       </c>
       <c r="Y80" s="9">
         <f t="shared" si="2"/>
@@ -4118,62 +4112,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C3:AA61"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.15234375" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.15234375" style="8"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="8"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -4190,75 +4184,75 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>0</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -4274,8 +4268,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.3</v>
       </c>
       <c r="E12" s="2">
@@ -4286,18 +4280,18 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>-0.1</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -4308,7 +4302,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -4325,7 +4319,7 @@
       <c r="K16" s="6"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -4337,7 +4331,7 @@
       <c r="K17" s="6"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -4349,7 +4343,7 @@
       <c r="K18" s="6"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
@@ -4361,14 +4355,14 @@
       <c r="K19" s="6"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.45">
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
         <v>33</v>
       </c>
@@ -4378,7 +4372,7 @@
       <c r="K21" s="6"/>
       <c r="O21" s="9"/>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
         <v>34</v>
       </c>
@@ -4386,7 +4380,7 @@
       <c r="K22" s="6"/>
       <c r="O22" s="9"/>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C23" t="str">
         <f t="array" ref="C23:C25">TRANSPOSE(D4:F4)</f>
         <v>google</v>
@@ -4398,7 +4392,7 @@
       <c r="K23" s="6"/>
       <c r="O23" s="9"/>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C24" t="str">
         <v>amazon</v>
       </c>
@@ -4409,7 +4403,7 @@
       <c r="K24" s="6"/>
       <c r="O24" s="9"/>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C25" t="str">
         <v>starbucks</v>
       </c>
@@ -4419,11 +4413,11 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C27" s="4" t="str">
         <f>_xll.xPutBaskets(C23:C25,D23:D25,D30,D32:F32,"bkt")</f>
         <v>bkt</v>
@@ -4431,15 +4425,15 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
         <v>35</v>
       </c>
@@ -4449,18 +4443,18 @@
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="M31" t="s">
         <v>31</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="24">
         <f>E32*EXP(1.5%)</f>
         <v>101.51130646157189</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
         <v>36</v>
       </c>
@@ -4468,7 +4462,7 @@
         <f>0.9*E32</f>
         <v>90</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="24">
         <f>E8</f>
         <v>100</v>
       </c>
@@ -4483,15 +4477,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="11"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="J33" s="6"/>
       <c r="K33" s="5"/>
       <c r="L33" s="8"/>
-      <c r="M33" s="24" t="e">
+      <c r="M33" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N33,,Q33*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4499,12 +4493,12 @@
         <f t="array" ref="N33:N35">TRANSPOSE(D32:F32)</f>
         <v>90</v>
       </c>
-      <c r="P33" s="22" t="str">
+      <c r="P33" s="21" t="str">
         <f t="array" ref="P33:W42">_xll.xValue(D16,C27,TRUE,,,500000,TRUE)</f>
         <v>basket strike 90.00</v>
       </c>
       <c r="Q33">
-        <v>12.962626451582683</v>
+        <v>12.962626451582681</v>
       </c>
       <c r="R33" t="e">
         <v>#N/A</v>
@@ -4532,13 +4526,13 @@
         <v>11.78353772595541</v>
       </c>
     </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="11"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="L34" s="8"/>
-      <c r="M34" s="24" t="e">
+      <c r="M34" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N34,,Q34*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4577,15 +4571,15 @@
         <v>5.8600268386718684</v>
       </c>
     </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="11"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="J35" s="6"/>
       <c r="K35" s="5"/>
       <c r="L35" s="8"/>
-      <c r="M35" s="24" t="e">
+      <c r="M35" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N35,,Q35*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4596,7 +4590,7 @@
         <v>basket strike 110.00</v>
       </c>
       <c r="Q35">
-        <v>2.9024499984701597</v>
+        <v>2.9024499984701593</v>
       </c>
       <c r="R35" t="e">
         <v>#N/A</v>
@@ -4624,7 +4618,7 @@
         <v>2.4506311356786377</v>
       </c>
     </row>
-    <row r="36" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="8"/>
@@ -4654,7 +4648,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="P37" t="e">
@@ -4682,13 +4676,13 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="L38" t="s">
         <v>37</v>
       </c>
-      <c r="M38" s="23" t="e">
+      <c r="M38" s="22" t="e">
         <f ca="1">M34</f>
         <v>#NAME?</v>
       </c>
@@ -4717,7 +4711,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -4759,7 +4753,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4794,7 +4788,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -4829,7 +4823,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -4864,7 +4858,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -4875,7 +4869,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -4886,7 +4880,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -4897,7 +4891,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -4908,7 +4902,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -4919,7 +4913,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -4930,7 +4924,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -4941,7 +4935,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -4952,7 +4946,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -4963,7 +4957,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -4974,7 +4968,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4985,7 +4979,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4996,7 +4990,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -5007,7 +5001,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -5018,7 +5012,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -5029,7 +5023,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -5040,7 +5034,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -5051,7 +5045,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -5062,7 +5056,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -5082,64 +5076,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C3:Y104"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.15234375" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.15234375" style="8"/>
-    <col min="13" max="13" width="37.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.69140625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="8"/>
+    <col min="13" max="13" width="37.53125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>0</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.01</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.25</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -5156,76 +5150,76 @@
         <v>luckin</v>
       </c>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
-      <c r="N7" s="24"/>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>43.71</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>63.8</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>26.96</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.45</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.5</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.1</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.5</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -5233,38 +5227,38 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <f ca="1">D12</f>
+        <f>D12</f>
         <v>0.5</v>
       </c>
       <c r="F11">
-        <f ca="1">D13</f>
+        <f>D13</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.5</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12">
-        <f ca="1">E13</f>
+        <f>E13</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.2</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.2</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -5275,12 +5269,12 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="4" t="str">
-        <f ca="1">_xll.xPutDLM(D4:F4,D8:F8,D9:F9,D10:F10,D5,H4:J4,H7:H8,I7:K8,D11:F13,D6,"dlm")</f>
+        <f>_xll.xPutDLM(D4:F4,D8:F8,D9:F9,D10:F10,D5,H4:J4,H7:H8,I7:K8,D11:F13,D6,"dlm")</f>
         <v>dlm</v>
       </c>
       <c r="E16" s="4"/>
@@ -5291,7 +5285,7 @@
       <c r="K16" s="6"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -5303,7 +5297,7 @@
       <c r="K17" s="6"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5315,17 +5309,17 @@
       <c r="K18" s="6"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>43.71</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="11">
         <v>63.8</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <v>26.96</v>
       </c>
       <c r="G19" s="4"/>
@@ -5341,7 +5335,7 @@
       </c>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C20" t="s">
         <v>35</v>
       </c>
@@ -5360,7 +5354,7 @@
       </c>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
         <v>40</v>
       </c>
@@ -5373,11 +5367,11 @@
       <c r="K21" s="6"/>
       <c r="O21" s="9"/>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C22" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <v>1</v>
       </c>
       <c r="H22"/>
@@ -5385,11 +5379,11 @@
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>0.76</v>
       </c>
       <c r="H23"/>
@@ -5397,11 +5391,11 @@
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>0.36</v>
       </c>
       <c r="H24"/>
@@ -5409,7 +5403,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C25" t="s">
         <v>43</v>
       </c>
@@ -5421,11 +5415,11 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="N25" s="1">
-        <f ca="1">N27-N26</f>
+        <f>N27-N26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
@@ -5434,10 +5428,10 @@
         <v>0.96495976051676235</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C27" s="4"/>
       <c r="D27" t="str">
-        <f ca="1">_xll.xPutAutocall(D4:F4,D19:F19,D20,D21,D22,D23,D24,D25,"autocall")</f>
+        <f>_xll.xPutAutocall(D4:F4,D19:F19,D20,D21,D22,D23,D24,D25,"autocall")</f>
         <v>autocall</v>
       </c>
       <c r="H27"/>
@@ -5445,61 +5439,49 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="M27" s="4" t="str">
-        <f t="array" aca="1" ref="M27:Y46" ca="1">_xll.xValue(D16,D27,TRUE,,,N19,N20)</f>
+        <f t="array" ref="M27:Y46">_xll.xValue(D16,D27,TRUE,,,N19,N20)</f>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N27" s="6">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y27" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.45">
       <c r="D28" t="str">
-        <f ca="1">_xll.xPayoffIds(D27)</f>
+        <f>_xll.xPayoffIds(D27)</f>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="H28"/>
@@ -5507,635 +5489,492 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="M28" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N28" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y28" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="M29" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N29" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y29" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="M30" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N30" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y30" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="M31" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N31" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y31" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="M32" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N32" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y32" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="M33" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N33" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y33" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="M34" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N34" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y34" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="M35" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N35" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y35" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="M36" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N36" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y36" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="M37" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N37" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y37" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
-      <c r="M38" s="27" t="str">
-        <f ca="1"/>
+      <c r="M38" s="26" t="str">
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N38" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y38" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -6146,59 +5985,46 @@
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="M39" s="5" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N39" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y39" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="40" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -6209,59 +6035,46 @@
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="M40" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N40" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y40" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -6272,59 +6085,46 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
       <c r="M41" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N41" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y41" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -6335,59 +6135,46 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="M42" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N42" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y42" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -6398,59 +6185,46 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="M43" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N43" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y43" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -6461,59 +6235,46 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
       <c r="M44" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N44" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y44" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -6524,59 +6285,46 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="M45" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N45" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y45" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -6587,59 +6335,46 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="M46" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N46" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y46" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -6650,7 +6385,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -6661,15 +6396,14 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="M48" s="4" t="str">
-        <f t="array" aca="1" ref="M48:N104" ca="1">_xll.xAADrisk(D16,D27,D28,TRUE,,,N19,N20)</f>
+        <f t="array" ref="M48:N104">_xll.xAADrisk(D16,D27,D28,TRUE,,,N19,N20)</f>
         <v>value</v>
       </c>
       <c r="N48" s="8">
-        <f ca="1"/>
-        <v>0.96495976051676247</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.4">
+        <v>0.96495976051676258</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -6683,15 +6417,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="str">
-        <f ca="1"/>
         <v>disc rate</v>
       </c>
-      <c r="N49" s="24">
-        <f ca="1"/>
-        <v>-0.1147608559187607</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N49" s="23">
+        <v>-0.11476085591875967</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -6705,15 +6437,13 @@
         <v>1</v>
       </c>
       <c r="M50" t="str">
-        <f ca="1"/>
         <v>spot uber</v>
       </c>
       <c r="N50" s="8">
-        <f ca="1"/>
-        <v>8.4753531785410605E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.4">
+        <v>8.4753531785410681E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -6727,15 +6457,13 @@
         <v>2</v>
       </c>
       <c r="M51" t="str">
-        <f ca="1"/>
         <v>spot lyft</v>
       </c>
-      <c r="N51" s="31">
-        <f ca="1"/>
-        <v>8.2817410998347761E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N51" s="30">
+        <v>8.2817410998347501E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -6749,15 +6477,13 @@
         <v>3</v>
       </c>
       <c r="M52" t="str">
-        <f ca="1"/>
         <v>spot luckin</v>
       </c>
       <c r="N52" s="8">
-        <f ca="1"/>
-        <v>4.3564639889824208E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.4">
+        <v>4.3564639889824277E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -6771,15 +6497,13 @@
         <v>4</v>
       </c>
       <c r="M53" t="str">
-        <f ca="1"/>
         <v>repo spread uber</v>
       </c>
-      <c r="N53" s="24">
-        <f ca="1"/>
-        <v>-2.858083270914898E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N53" s="23">
+        <v>-2.8580832709148993E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -6793,15 +6517,13 @@
         <v>5</v>
       </c>
       <c r="M54" t="str">
-        <f ca="1"/>
         <v>repo spread lyft</v>
       </c>
-      <c r="N54" s="24">
-        <f ca="1"/>
+      <c r="N54" s="23">
         <v>-7.0428767478183302E-2</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -6815,15 +6537,13 @@
         <v>6</v>
       </c>
       <c r="M55" t="str">
-        <f ca="1"/>
         <v>repo spread luckin</v>
       </c>
-      <c r="N55" s="24">
-        <f ca="1"/>
+      <c r="N55" s="23">
         <v>-7.9014360190003866E-2</v>
       </c>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -6837,15 +6557,13 @@
         <v>7</v>
       </c>
       <c r="M56" t="str">
-        <f ca="1"/>
         <v>div uber 0.25</v>
       </c>
-      <c r="N56" s="24">
-        <f ca="1"/>
-        <v>-5.89291818494658E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N56" s="23">
+        <v>-5.8929181849465793E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -6859,15 +6577,13 @@
         <v>8</v>
       </c>
       <c r="M57" t="str">
-        <f ca="1"/>
         <v>div lyft 0.25</v>
       </c>
-      <c r="N57" s="24">
-        <f ca="1"/>
-        <v>-0.11769615504528579</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N57" s="23">
+        <v>-0.11769615504528576</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -6881,15 +6597,13 @@
         <v>9</v>
       </c>
       <c r="M58" t="str">
-        <f ca="1"/>
         <v>div luckin 0.25</v>
       </c>
-      <c r="N58" s="24">
-        <f ca="1"/>
-        <v>-0.14837682083622522</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N58" s="23">
+        <v>-0.14837682083622525</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -6903,15 +6617,13 @@
         <v>10</v>
       </c>
       <c r="M59" t="str">
-        <f ca="1"/>
         <v>div uber 0.75</v>
       </c>
-      <c r="N59" s="24">
-        <f ca="1"/>
+      <c r="N59" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -6925,15 +6637,13 @@
         <v>11</v>
       </c>
       <c r="M60" t="str">
-        <f ca="1"/>
         <v>div lyft 0.75</v>
       </c>
-      <c r="N60" s="24">
-        <f ca="1"/>
+      <c r="N60" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -6947,471 +6657,383 @@
         <v>12</v>
       </c>
       <c r="M61" t="str">
-        <f ca="1"/>
         <v>div luckin 0.75</v>
       </c>
-      <c r="N61" s="24">
-        <f ca="1"/>
+      <c r="N61" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.45">
       <c r="L62">
         <v>13</v>
       </c>
       <c r="M62" t="str">
-        <f ca="1"/>
         <v>ATM uber</v>
       </c>
-      <c r="N62" s="24">
-        <f ca="1"/>
-        <v>-7.2689795180755912E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.4">
-      <c r="L63" s="28">
+      <c r="N62" s="23">
+        <v>-7.2689795180755815E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="L63" s="27">
         <v>14</v>
       </c>
-      <c r="M63" s="28" t="str">
-        <f ca="1"/>
+      <c r="M63" s="27" t="str">
         <v>ATM lyft</v>
       </c>
-      <c r="N63" s="29">
-        <f ca="1"/>
-        <v>-0.15504777779332335</v>
-      </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N63" s="28">
+        <v>-0.15504777779332363</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.45">
       <c r="L64">
         <v>15</v>
       </c>
       <c r="M64" t="str">
-        <f ca="1"/>
         <v>ATM luckin</v>
       </c>
-      <c r="N64" s="24">
-        <f ca="1"/>
-        <v>-0.16802184695029357</v>
-      </c>
-    </row>
-    <row r="65" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N64" s="23">
+        <v>-0.16802184695029398</v>
+      </c>
+    </row>
+    <row r="65" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L65">
         <v>16</v>
       </c>
       <c r="M65" t="str">
-        <f ca="1"/>
         <v>skew uber</v>
       </c>
-      <c r="N65" s="26">
-        <f ca="1"/>
-        <v>2.6636703664252876E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="12:14" x14ac:dyDescent="0.4">
-      <c r="L66" s="28">
+      <c r="N65" s="25">
+        <v>2.6636703664253282E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="12:14" x14ac:dyDescent="0.45">
+      <c r="L66" s="27">
         <v>17</v>
       </c>
-      <c r="M66" s="28" t="str">
-        <f ca="1"/>
+      <c r="M66" s="27" t="str">
         <v>skew lyft</v>
       </c>
-      <c r="N66" s="30">
-        <f ca="1"/>
-        <v>5.9137145144274379E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N66" s="29">
+        <v>5.9137145144274088E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L67">
         <v>18</v>
       </c>
       <c r="M67" t="str">
-        <f ca="1"/>
         <v>skew luckin</v>
       </c>
-      <c r="N67" s="24">
-        <f ca="1"/>
-        <v>7.4092312588810466E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N67" s="23">
+        <v>7.4092312588808967E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L68">
         <v>19</v>
       </c>
       <c r="M68" t="str">
-        <f ca="1"/>
         <v>correl lyft uber</v>
       </c>
-      <c r="N68" s="24">
-        <f ca="1"/>
-        <v>8.2534884478533584E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N68" s="23">
+        <v>8.2534884478533896E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L69">
         <v>20</v>
       </c>
       <c r="M69" t="str">
-        <f ca="1"/>
         <v>correl luckin uber</v>
       </c>
-      <c r="N69" s="24">
-        <f ca="1"/>
-        <v>6.0410904294307347E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N69" s="23">
+        <v>6.0410904294307321E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L70">
         <v>21</v>
       </c>
       <c r="M70" t="str">
-        <f ca="1"/>
         <v>correl luckin lyft</v>
       </c>
-      <c r="N70" s="24">
-        <f ca="1"/>
-        <v>1.7588752186493046E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N70" s="23">
+        <v>1.7588752186493039E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L71">
         <v>22</v>
       </c>
       <c r="M71" t="str">
-        <f ca="1"/>
         <v>lambda</v>
       </c>
-      <c r="N71" s="24">
-        <f ca="1"/>
-        <v>3.0707491088887599E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N71" s="23">
+        <v>3.0707491088887613E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M72" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N72" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="73" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M73" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N73" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="74" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M74" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N74" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="75" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M75" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N75" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="76" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="76" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M76" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N76" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="77" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M77" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N77" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="78" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M78" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N78" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="79" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M79" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N79" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="80" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M80" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N80" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="81" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M81" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N81" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M82" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N82" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="83" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M83" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N83" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M84" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N84" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="85" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M85" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N85" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="86" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M86" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N86" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="87" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M87" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N87" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="88" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M88" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N88" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="89" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M89" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N89" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="90" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M90" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N90" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="91" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M91" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N91" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="92" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M92" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N92" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="93" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M93" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N93" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="94" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M94" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N94" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="95" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="95" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M95" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N95" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="96" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="96" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M96" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N96" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="97" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M97" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N97" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="98" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M98" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N98" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="99" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M99" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N99" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="100" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M100" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N100" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="101" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M101" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N101" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="102" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="102" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M102" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N102" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="103" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="103" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M103" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N103" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="104" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="104" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M104" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N104" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -7424,7 +7046,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testDLM.xlsx
+++ b/testDLM.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bernardo\dev\repos\CompFinance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4581E5D5-4A14-4B71-A1F8-94B2AA783AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3741E151-C964-4A47-A75D-2385AF01C45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17769" yWindow="6146" windowWidth="17280" windowHeight="10071" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18154" yWindow="5760" windowWidth="17280" windowHeight="10071" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1 (3)" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1 (4)" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -7041,13 +7040,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/testDLM.xlsx
+++ b/testDLM.xlsx
@@ -1,33 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antoine\Source\Repos\CompFinance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bernardo\dev\my_repos\CompFinance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83F81EB-3DBF-4DAF-B4A2-0847A936B429}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCE1F1-2E9E-4BE8-A392-78740350B748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="44092" windowHeight="24292" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1 (3)" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1 (4)" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcMode="manual" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -188,8 +182,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -329,7 +323,7 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -338,29 +332,28 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="3"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="6" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="6" borderId="0" xfId="7" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="7" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="5"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -694,67 +687,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:AA61"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3046875" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3046875" style="8"/>
-    <col min="16" max="16" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="8"/>
+    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.45">
       <c r="T3" t="str">
         <f>_xll.xPutMultiStats(D4:F4,1,2,"stats")</f>
         <v>stats</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>0.01</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.25</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -764,75 +757,75 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.5</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -854,8 +847,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.8</v>
       </c>
       <c r="E12" s="2">
@@ -872,11 +865,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.5</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.7</v>
       </c>
       <c r="F13" s="2">
@@ -889,7 +882,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -900,7 +893,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -921,10 +914,10 @@
       <c r="R16" s="9"/>
       <c r="T16" t="str">
         <f t="array" ref="T16:V30">_xll.xValue(D16,T3,U12,,,U13,U11)</f>
-        <v>google 0.50 0.50</v>
+        <v>google 1.00 2.00</v>
       </c>
       <c r="U16" s="9">
-        <v>50.250643505236695</v>
+        <v>51.01016454437783</v>
       </c>
       <c r="V16" t="e">
         <v>#N/A</v>
@@ -935,7 +928,7 @@
       </c>
       <c r="Y16" s="9"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -950,10 +943,10 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="T17" t="str">
-        <v>amazon 0.50 0.50</v>
+        <v>amazon 1.00 2.00</v>
       </c>
       <c r="U17" s="9">
-        <v>95.476143613249917</v>
+        <v>103.04535496549822</v>
       </c>
       <c r="V17" t="e">
         <v>#N/A</v>
@@ -964,7 +957,7 @@
       </c>
       <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C18" s="3" t="str">
         <f t="array" ref="C18:H30">_xll.xViewDLM(D16)</f>
         <v/>
@@ -992,10 +985,10 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="T18" t="str">
-        <v>starbucks 0.50 0.50</v>
+        <v>starbucks 1.00 2.00</v>
       </c>
       <c r="U18" s="9">
-        <v>22.612857494939018</v>
+        <v>25.633417938570016</v>
       </c>
       <c r="V18" t="e">
         <v>#N/A</v>
@@ -1006,7 +999,7 @@
       </c>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="str">
         <v>google</v>
       </c>
@@ -1014,7 +1007,7 @@
         <v>subnormal</v>
       </c>
       <c r="E19" s="5">
-        <v>66.666666666666671</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="F19" s="5">
         <v>0.60000000000000009</v>
@@ -1033,17 +1026,17 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="T19" t="str">
-        <v>google google 0.50 0.50</v>
+        <v>google google 1.00 2.00</v>
       </c>
       <c r="U19" s="9">
-        <v>2578.2661789716112</v>
+        <v>2717.4906033510347</v>
       </c>
       <c r="V19" t="e">
         <v>#N/A</v>
       </c>
       <c r="Y19" s="9"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C20" t="str">
         <v>amazon</v>
       </c>
@@ -1069,10 +1062,10 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="T20" t="str">
-        <v>amazon google 0.50 0.50</v>
+        <v>amazon google 1.00 2.00</v>
       </c>
       <c r="U20" s="9">
-        <v>4819.5123831342207</v>
+        <v>5382.1604930710319</v>
       </c>
       <c r="V20" t="e">
         <v>#N/A</v>
@@ -1080,7 +1073,7 @@
       <c r="Y20" s="9"/>
       <c r="AA20" s="7"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C21" t="str">
         <v>starbucks</v>
       </c>
@@ -1088,7 +1081,7 @@
         <v>subnormal</v>
       </c>
       <c r="E21" s="7">
-        <v>33.333333333333329</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="F21" s="7">
         <v>0.75</v>
@@ -1106,17 +1099,17 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="T21" t="str">
-        <v>amazon amazon 0.50 0.50</v>
+        <v>amazon amazon 1.00 2.00</v>
       </c>
       <c r="U21" s="9">
-        <v>9224.8911323503617</v>
+        <v>10852.823468633802</v>
       </c>
       <c r="V21" t="e">
         <v>#N/A</v>
       </c>
       <c r="Y21" s="9"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C22" t="e">
         <v>#N/A</v>
       </c>
@@ -1142,10 +1135,10 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="T22" t="str">
-        <v>starbucks google 0.50 0.50</v>
+        <v>starbucks google 1.00 2.00</v>
       </c>
       <c r="U22" s="9">
-        <v>1140.3114289264086</v>
+        <v>1350.5556695677483</v>
       </c>
       <c r="V22" t="e">
         <v>#N/A</v>
@@ -1153,7 +1146,7 @@
       <c r="Y22" s="9"/>
       <c r="AA22" s="7"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C23" t="e">
         <v>#N/A</v>
       </c>
@@ -1179,10 +1172,10 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="T23" t="str">
-        <v>starbucks amazon 0.50 0.50</v>
+        <v>starbucks amazon 1.00 2.00</v>
       </c>
       <c r="U23" s="9">
-        <v>2153.0412675187622</v>
+        <v>2712.5561131123955</v>
       </c>
       <c r="V23" t="e">
         <v>#N/A</v>
@@ -1190,7 +1183,7 @@
       <c r="Y23" s="9"/>
       <c r="AA23" s="7"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C24" t="e">
         <v>#N/A</v>
       </c>
@@ -1216,17 +1209,17 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="T24" t="str">
-        <v>starbucks starbucks 0.50 0.50</v>
+        <v>starbucks starbucks 1.00 2.00</v>
       </c>
       <c r="U24" s="9">
-        <v>548.65903254552404</v>
+        <v>706.68175945278654</v>
       </c>
       <c r="V24" t="e">
         <v>#N/A</v>
       </c>
       <c r="Y24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C25" t="e">
         <v>#N/A</v>
       </c>
@@ -1247,17 +1240,17 @@
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
-      <c r="T25" t="str">
-        <v>google 1.00 1.00</v>
-      </c>
-      <c r="U25">
-        <v>46.462565020808249</v>
+      <c r="T25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U25" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V25" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C26" t="e">
         <v>#N/A</v>
       </c>
@@ -1278,17 +1271,17 @@
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
-      <c r="T26" t="str">
-        <v>amazon 1.00 1.00</v>
-      </c>
-      <c r="U26">
-        <v>95.954601969190364</v>
+      <c r="T26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V26" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C27" t="e">
         <v>#N/A</v>
       </c>
@@ -1309,17 +1302,17 @@
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
-      <c r="T27" t="str">
-        <v>starbucks 1.00 1.00</v>
-      </c>
-      <c r="U27">
-        <v>22.72662860436218</v>
+      <c r="T27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U27" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V27" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C28" t="e">
         <v>#N/A</v>
       </c>
@@ -1340,17 +1333,17 @@
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
-      <c r="T28" t="str">
-        <v>google google 1.00 1.00</v>
-      </c>
-      <c r="U28">
-        <v>2293.5689471641099</v>
+      <c r="T28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U28" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V28" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C29" t="e">
         <v>#N/A</v>
       </c>
@@ -1371,17 +1364,17 @@
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
-      <c r="T29" t="str">
-        <v>amazon google 1.00 1.00</v>
-      </c>
-      <c r="U29">
-        <v>4505.2650985858845</v>
+      <c r="T29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U29" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V29" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C30" t="e">
         <v>#N/A</v>
       </c>
@@ -1402,21 +1395,21 @@
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
-      <c r="T30" t="str">
-        <v>amazon amazon 1.00 1.00</v>
-      </c>
-      <c r="U30">
-        <v>9427.265093697164</v>
+      <c r="T30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="V30" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>19</v>
       </c>
@@ -1438,7 +1431,7 @@
       <c r="J32" s="6"/>
       <c r="K32" s="6"/>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33">
         <f t="array" ref="B33:B35">TRANSPOSE(D8:F8)</f>
         <v>50</v>
@@ -1453,19 +1446,19 @@
       </c>
       <c r="E33" s="7">
         <f>IF(F19=0,E19/D33,E19)</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="F33" s="11">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="F33" s="7">
         <f>IF(D19="subnormal",E33-B33,E33+B33)</f>
-        <v>16.666666666666671</v>
+        <v>16.666666666666657</v>
       </c>
       <c r="G33" s="7">
         <f>F33^2*(EXP(D33^2)-1)</f>
-        <v>120.36928182231684</v>
+        <v>120.36928182231664</v>
       </c>
       <c r="H33" s="7">
         <f>SQRT(G33)</f>
-        <v>10.971293534598226</v>
+        <v>10.971293534598217</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -1473,7 +1466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>100</v>
       </c>
@@ -1489,7 +1482,7 @@
         <f>IF(F20=0,E20/D34,E20)</f>
         <v>200.00000000000006</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="7">
         <f>IF(D20="subnormal",E34-B34,E34+B34)</f>
         <v>300.00000000000006</v>
       </c>
@@ -1524,14 +1517,14 @@
       </c>
       <c r="P34" s="10">
         <f>N34*F33*F34*(EXP(N34*L34*D33*D34)-1)</f>
-        <v>125.88810517129463</v>
+        <v>125.88810517129451</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R34" s="10">
         <f>W49</f>
-        <v>21.774727170018195</v>
+        <v>125.79998074714695</v>
       </c>
       <c r="V34" t="str">
         <f t="array" ref="V34:V36">TRANSPOSE(D4:F4)</f>
@@ -1539,10 +1532,10 @@
       </c>
       <c r="W34" s="9">
         <f>U16</f>
-        <v>50.250643505236695</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.4">
+        <v>51.01016454437783</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>25</v>
       </c>
@@ -1556,19 +1549,19 @@
       </c>
       <c r="E35" s="7">
         <f>IF(F21=0,E21/D35,E21)</f>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="F35" s="11">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="F35" s="7">
         <f>IF(D21="subnormal",E35-B35,E35+B35)</f>
-        <v>8.3333333333333286</v>
+        <v>8.3333333333333357</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>52.434351177798455</v>
+        <v>52.43435117779854</v>
       </c>
       <c r="H35" s="7">
         <f>SQRT(G35)</f>
-        <v>7.241156756886185</v>
+        <v>7.2411567568861912</v>
       </c>
       <c r="J35" s="6" t="str">
         <f>C34&amp;"/"&amp;C35</f>
@@ -1593,24 +1586,24 @@
       </c>
       <c r="P35" s="10">
         <f>N35*F34*F35*(EXP(N35*L35*D34*D35)-1)</f>
-        <v>71.610617912915259</v>
+        <v>71.61061791291533</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R35" s="10">
         <f>Y49</f>
-        <v>-5.947162173990364</v>
+        <v>71.151462653478575</v>
       </c>
       <c r="V35" t="str">
         <v>amazon</v>
       </c>
       <c r="W35" s="9">
         <f>U17</f>
-        <v>95.476143613249917</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.4">
+        <v>103.04535496549822</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J36" s="6" t="s">
         <v>26</v>
       </c>
@@ -1640,28 +1633,28 @@
       </c>
       <c r="R36" s="10">
         <f>W50</f>
-        <v>4.0007883135083375</v>
+        <v>42.990802686485495</v>
       </c>
       <c r="V36" t="str">
         <v>starbucks</v>
       </c>
       <c r="W36" s="9">
         <f>U18</f>
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.633417938570016</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="W38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1673,16 +1666,16 @@
       <c r="K39" s="6"/>
       <c r="W39" s="7">
         <f t="array" ref="W39:Y39">TRANSPOSE(U41:U43)</f>
-        <v>50.250643505236695</v>
+        <v>51.01016454437783</v>
       </c>
       <c r="X39" s="7">
-        <v>95.476143613249917</v>
+        <v>103.04535496549822</v>
       </c>
       <c r="Y39" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.633417938570016</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -1703,7 +1696,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1715,7 +1708,7 @@
       <c r="K41" s="6"/>
       <c r="U41" s="7">
         <f t="array" ref="U41:U43">W34:W36</f>
-        <v>50.250643505236695</v>
+        <v>51.01016454437783</v>
       </c>
       <c r="V41" t="str">
         <f t="array" ref="V41:V43">V34:V36</f>
@@ -1723,18 +1716,18 @@
       </c>
       <c r="W41" s="9">
         <f>U19</f>
-        <v>2578.2661789716112</v>
+        <v>2717.4906033510347</v>
       </c>
       <c r="X41" s="9">
         <f>W42</f>
-        <v>4819.5123831342207</v>
+        <v>5382.1604930710319</v>
       </c>
       <c r="Y41" s="9">
         <f>W43</f>
-        <v>1140.3114289264086</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.4">
+        <v>1350.5556695677483</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -1745,25 +1738,25 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="U42" s="7">
-        <v>95.476143613249917</v>
+        <v>103.04535496549822</v>
       </c>
       <c r="V42" t="str">
         <v>amazon</v>
       </c>
       <c r="W42" s="9">
         <f>U20</f>
-        <v>4819.5123831342207</v>
+        <v>5382.1604930710319</v>
       </c>
       <c r="X42" s="9">
         <f>U21</f>
-        <v>9224.8911323503617</v>
+        <v>10852.823468633802</v>
       </c>
       <c r="Y42" s="9">
         <f>X43</f>
-        <v>2153.0412675187622</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.4">
+        <v>2712.5561131123955</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -1774,25 +1767,25 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="U43" s="7">
-        <v>22.612857494939018</v>
+        <v>25.633417938570016</v>
       </c>
       <c r="V43" t="str">
         <v>starbucks</v>
       </c>
       <c r="W43" s="9">
         <f>U22</f>
-        <v>1140.3114289264086</v>
+        <v>1350.5556695677483</v>
       </c>
       <c r="X43" s="9">
         <f>U23</f>
-        <v>2153.0412675187622</v>
+        <v>2712.5561131123955</v>
       </c>
       <c r="Y43" s="9">
         <f>U24</f>
-        <v>548.65903254552404</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.4">
+        <v>706.68175945278654</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -1803,7 +1796,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -1817,7 +1810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -1829,16 +1822,16 @@
       <c r="K46" s="6"/>
       <c r="W46" s="7">
         <f t="array" ref="W46:Y46">W39:Y39</f>
-        <v>50.250643505236695</v>
+        <v>51.01016454437783</v>
       </c>
       <c r="X46" s="7">
-        <v>95.476143613249917</v>
+        <v>103.04535496549822</v>
       </c>
       <c r="Y46" s="7">
-        <v>22.612857494939018</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.4">
+        <v>25.633417938570016</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -1859,7 +1852,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -1871,7 +1864,7 @@
       <c r="K48" s="6"/>
       <c r="U48" s="7">
         <f t="array" ref="U48:U50">U41:U43</f>
-        <v>50.250643505236695</v>
+        <v>51.01016454437783</v>
       </c>
       <c r="V48" t="str">
         <f t="array" ref="V48:V50">V41:V43</f>
@@ -1879,18 +1872,18 @@
       </c>
       <c r="W48" s="9">
         <f>W41-$U48*W$46</f>
-        <v>53.139006281224283</v>
+        <v>115.45371650653351</v>
       </c>
       <c r="X48" s="9">
         <f t="shared" ref="X48:Y48" si="1">X41-$U48*X$46</f>
-        <v>21.774727170018195</v>
+        <v>125.79998074714695</v>
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.4">
+        <v>42.990802686485495</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -1901,25 +1894,25 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
       <c r="U49" s="7">
-        <v>95.476143613249917</v>
+        <v>103.04535496549822</v>
       </c>
       <c r="V49" t="str">
         <v>amazon</v>
       </c>
       <c r="W49" s="9">
         <f t="shared" ref="W49:Y49" si="2">W42-$U49*W$46</f>
-        <v>21.774727170018195</v>
+        <v>125.79998074714695</v>
       </c>
       <c r="X49" s="9">
         <f t="shared" si="2"/>
-        <v>109.19713309243889</v>
+        <v>234.47828866827331</v>
       </c>
       <c r="Y49" s="9">
         <f t="shared" si="2"/>
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.4">
+        <v>71.151462653478575</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -1930,25 +1923,25 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
       <c r="U50" s="7">
-        <v>22.612857494939018</v>
+        <v>25.633417938570016</v>
       </c>
       <c r="V50" t="str">
         <v>starbucks</v>
       </c>
       <c r="W50" s="9">
         <f t="shared" ref="W50:Y50" si="3">W43-$U50*W$46</f>
-        <v>4.0007883135083375</v>
+        <v>42.990802686485495</v>
       </c>
       <c r="X50" s="9">
         <f t="shared" si="3"/>
-        <v>-5.947162173990364</v>
+        <v>71.151462653478575</v>
       </c>
       <c r="Y50" s="9">
         <f t="shared" si="3"/>
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.4">
+        <v>49.609644239383442</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -1959,7 +1952,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -1973,7 +1966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -1985,18 +1978,18 @@
       <c r="K53" s="6"/>
       <c r="W53" s="7">
         <f>SQRT(W48)</f>
-        <v>7.2896506282005236</v>
+        <v>10.744939111346024</v>
       </c>
       <c r="X53" s="7">
         <f>SQRT(X49)</f>
-        <v>10.449743207009391</v>
+        <v>15.312683914594244</v>
       </c>
       <c r="Y53" s="7">
         <f>SQRT(Y50)</f>
-        <v>6.1088221826391642</v>
-      </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.4">
+        <v>7.0434114063700299</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -2017,7 +2010,7 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -2029,11 +2022,11 @@
       <c r="K55" s="6"/>
       <c r="T55" s="10">
         <f>U55/W34</f>
-        <v>0.14506581646941213</v>
+        <v>0.21064309843576648</v>
       </c>
       <c r="U55" s="7">
         <f t="array" ref="U55:U57">TRANSPOSE(W53:Y53)</f>
-        <v>7.2896506282005236</v>
+        <v>10.744939111346024</v>
       </c>
       <c r="V55" t="str">
         <f t="array" ref="V55:V57">V48:V50</f>
@@ -2041,18 +2034,18 @@
       </c>
       <c r="W55" s="9">
         <f>W48/$U55/W$53</f>
-        <v>0.99999999999999989</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="X55" s="9">
         <f t="shared" ref="X55:Y55" si="4">X48/$U55/X$53</f>
-        <v>0.28585144347144498</v>
+        <v>0.7645841626823775</v>
       </c>
       <c r="Y55" s="9">
         <f t="shared" si="4"/>
-        <v>8.98424061952042E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.4">
+        <v>0.56805258282582716</v>
+      </c>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -2064,28 +2057,28 @@
       <c r="K56" s="6"/>
       <c r="T56" s="10">
         <f>U56/W35</f>
-        <v>0.10944873568981481</v>
+        <v>0.14860139906084321</v>
       </c>
       <c r="U56" s="7">
-        <v>10.449743207009391</v>
+        <v>15.312683914594244</v>
       </c>
       <c r="V56" t="str">
         <v>amazon</v>
       </c>
       <c r="W56" s="9">
         <f t="shared" ref="W56:Y56" si="5">W49/$U56/W$53</f>
-        <v>0.28585144347144503</v>
+        <v>0.76458416268237739</v>
       </c>
       <c r="X56" s="9">
         <f t="shared" si="5"/>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="Y56" s="9">
         <f t="shared" si="5"/>
-        <v>-9.3163689561357926E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.4">
+        <v>0.65970451754100423</v>
+      </c>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -2097,28 +2090,28 @@
       <c r="K57" s="6"/>
       <c r="T57" s="10">
         <f>U57/W36</f>
-        <v>0.27014817494898108</v>
+        <v>0.27477457057226734</v>
       </c>
       <c r="U57" s="7">
-        <v>6.1088221826391642</v>
+        <v>7.0434114063700299</v>
       </c>
       <c r="V57" t="str">
         <v>starbucks</v>
       </c>
       <c r="W57" s="9">
         <f t="shared" ref="W57:Y57" si="6">W50/$U57/W$53</f>
-        <v>8.9842406195204214E-2</v>
+        <v>0.56805258282582716</v>
       </c>
       <c r="X57" s="9">
         <f t="shared" si="6"/>
-        <v>-9.3163689561357926E-2</v>
+        <v>0.65970451754100423</v>
       </c>
       <c r="Y57" s="9">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -2129,7 +2122,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -2140,7 +2133,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -2151,7 +2144,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -2171,26 +2164,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:AA80"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.3046875" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3046875" style="8"/>
-    <col min="16" max="16" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="34.3828125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.15234375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="8"/>
+    <col min="16" max="16" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.45">
       <c r="X2" t="s">
         <v>30</v>
       </c>
@@ -2198,7 +2191,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
@@ -2213,26 +2206,26 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0.01</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>0.01</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>0.01</v>
       </c>
       <c r="T4" t="str">
@@ -2246,22 +2239,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -2278,75 +2271,75 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0.05</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0.08</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.05</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.5</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -2368,8 +2361,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.3</v>
       </c>
       <c r="E12" s="2">
@@ -2386,11 +2379,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>-0.1</v>
       </c>
       <c r="F13" s="2">
@@ -2403,7 +2396,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -2414,7 +2407,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -2444,14 +2437,14 @@
         <v>google 0.50 0.50</v>
       </c>
       <c r="U16" s="9">
-        <v>50.250643505236695</v>
-      </c>
-      <c r="V16" s="20">
+        <v>50.250643505236702</v>
+      </c>
+      <c r="V16" s="19">
         <v>50.00001772886462</v>
       </c>
       <c r="Y16" s="9"/>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -2475,14 +2468,14 @@
         <v>amazon 0.50 0.50</v>
       </c>
       <c r="U17" s="9">
-        <v>95.476143613249917</v>
-      </c>
-      <c r="V17" s="20">
+        <v>95.476143613249945</v>
+      </c>
+      <c r="V17" s="19">
         <v>99.999953429352431</v>
       </c>
       <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C18" s="3" t="str">
         <f t="array" ref="C18:H30">_xll.xViewDLM(D16)</f>
         <v/>
@@ -2521,12 +2514,12 @@
       <c r="U18" s="9">
         <v>22.612857494939018</v>
       </c>
-      <c r="V18" s="20">
+      <c r="V18" s="19">
         <v>25.000058902133254</v>
       </c>
       <c r="Y18" s="9"/>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="str">
         <v>google</v>
       </c>
@@ -2534,7 +2527,7 @@
         <v>subnormal</v>
       </c>
       <c r="E19" s="5">
-        <v>66.666666666666671</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="F19" s="5">
         <v>0.60000000000000009</v>
@@ -2561,16 +2554,16 @@
       <c r="U19" s="9">
         <v>2578.2661789716112</v>
       </c>
-      <c r="V19" s="20">
+      <c r="V19" s="19">
         <v>2554.7757267453712</v>
       </c>
       <c r="W19" s="7">
         <f>U19-U16*U16</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="Y19" s="9"/>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C20" t="str">
         <v>amazon</v>
       </c>
@@ -2604,17 +2597,17 @@
       <c r="U20" s="9">
         <v>4819.5123831342207</v>
       </c>
-      <c r="V20" s="20">
+      <c r="V20" s="19">
         <v>5022.445075340017</v>
       </c>
       <c r="W20" s="7">
         <f>U20-U16*U17</f>
-        <v>21.774727170018195</v>
+        <v>21.774727170015467</v>
       </c>
       <c r="Y20" s="9"/>
       <c r="AA20" s="7"/>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C21" t="str">
         <v>starbucks</v>
       </c>
@@ -2622,7 +2615,7 @@
         <v>subnormal</v>
       </c>
       <c r="E21" s="7">
-        <v>33.333333333333329</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="F21" s="7">
         <v>0.75</v>
@@ -2646,18 +2639,18 @@
         <v>amazon amazon 0.50 0.50</v>
       </c>
       <c r="U21" s="9">
-        <v>9224.8911323503617</v>
-      </c>
-      <c r="V21" s="20">
+        <v>9224.8911323503598</v>
+      </c>
+      <c r="V21" s="19">
         <v>10112.557083136648</v>
       </c>
       <c r="W21" s="7">
         <f>U21-U17*U17</f>
-        <v>109.19713309243889</v>
+        <v>109.19713309243161</v>
       </c>
       <c r="Y21" s="9"/>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C22" t="e">
         <v>#N/A</v>
       </c>
@@ -2691,17 +2684,17 @@
       <c r="U22" s="9">
         <v>1140.3114289264086</v>
       </c>
-      <c r="V22" s="20">
+      <c r="V22" s="19">
         <v>1253.1607732194359</v>
       </c>
       <c r="W22" s="7">
         <f>U22-U18*U16</f>
-        <v>4.0007883135083375</v>
+        <v>4.0007883135081101</v>
       </c>
       <c r="Y22" s="9"/>
       <c r="AA22" s="7"/>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C23" t="e">
         <v>#N/A</v>
       </c>
@@ -2735,17 +2728,17 @@
       <c r="U23" s="9">
         <v>2153.0412675187622</v>
       </c>
-      <c r="V23" s="20">
+      <c r="V23" s="19">
         <v>2495.3110817065335</v>
       </c>
       <c r="W23" s="7">
         <f>U23-U18*U17</f>
-        <v>-5.947162173990364</v>
+        <v>-5.9471621739908187</v>
       </c>
       <c r="Y23" s="9"/>
       <c r="AA23" s="7"/>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C24" t="e">
         <v>#N/A</v>
       </c>
@@ -2777,18 +2770,18 @@
         <v>starbucks starbucks 0.50 0.50</v>
       </c>
       <c r="U24" s="9">
-        <v>548.65903254552404</v>
-      </c>
-      <c r="V24" s="20">
+        <v>548.65903254552416</v>
+      </c>
+      <c r="V24" s="19">
         <v>647.55147391399305</v>
       </c>
       <c r="W24" s="7">
         <f>U24-U18*U18</f>
-        <v>37.317708459104324</v>
+        <v>37.317708459104438</v>
       </c>
       <c r="Y24" s="9"/>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C25" t="e">
         <v>#N/A</v>
       </c>
@@ -2827,21 +2820,21 @@
       <c r="U25" s="7">
         <v>46.462565020808249</v>
       </c>
-      <c r="V25" s="21">
+      <c r="V25" s="20">
         <v>50.000272818845943</v>
       </c>
-      <c r="X25" s="17" t="str">
+      <c r="X25" s="16" t="str">
         <f t="array" ref="X25:Z33">_xll.xValue(D16,T4,U12,,,U13,U11)</f>
         <v>google 1.00 1.00</v>
       </c>
-      <c r="Y25" s="18">
+      <c r="Y25" s="17">
         <v>46.462428396446704</v>
       </c>
-      <c r="Z25" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z25" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C26" t="e">
         <v>#N/A</v>
       </c>
@@ -2877,22 +2870,22 @@
         <v>amazon 1.00 1.00</v>
       </c>
       <c r="U26" s="7">
-        <v>95.954601969190364</v>
-      </c>
-      <c r="V26" s="21">
+        <v>95.954601969190392</v>
+      </c>
+      <c r="V26" s="20">
         <v>99.999834036142801</v>
       </c>
-      <c r="X26" s="17" t="str">
+      <c r="X26" s="16" t="str">
         <v>amazon 1.00 1.00</v>
       </c>
-      <c r="Y26" s="18">
-        <v>95.95469713213491</v>
-      </c>
-      <c r="Z26" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y26" s="17">
+        <v>95.954697132134939</v>
+      </c>
+      <c r="Z26" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C27" t="e">
         <v>#N/A</v>
       </c>
@@ -2928,22 +2921,22 @@
         <v>starbucks 1.00 1.00</v>
       </c>
       <c r="U27" s="7">
-        <v>22.72662860436218</v>
-      </c>
-      <c r="V27" s="21">
+        <v>22.726628604362176</v>
+      </c>
+      <c r="V27" s="20">
         <v>25.000388137689914</v>
       </c>
-      <c r="X27" s="17" t="str">
+      <c r="X27" s="16" t="str">
         <v>starbucks 1.00 1.00</v>
       </c>
-      <c r="Y27" s="18">
-        <v>22.726340449128799</v>
-      </c>
-      <c r="Z27" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y27" s="17">
+        <v>22.726340449128806</v>
+      </c>
+      <c r="Z27" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C28" t="e">
         <v>#N/A</v>
       </c>
@@ -2971,22 +2964,22 @@
         <v>google google 1.00 1.00</v>
       </c>
       <c r="U28" s="7">
-        <v>2293.5689471641099</v>
-      </c>
-      <c r="V28" s="21">
+        <v>2293.5689471641094</v>
+      </c>
+      <c r="V28" s="20">
         <v>2620.2864548711691</v>
       </c>
-      <c r="X28" s="17" t="str">
+      <c r="X28" s="16" t="str">
         <v>google google 1.00 1.00</v>
       </c>
-      <c r="Y28" s="18">
+      <c r="Y28" s="17">
         <v>2335.5669128384684</v>
       </c>
-      <c r="Z28" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z28" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C29" t="e">
         <v>#N/A</v>
       </c>
@@ -3014,22 +3007,22 @@
         <v>amazon google 1.00 1.00</v>
       </c>
       <c r="U29" s="7">
-        <v>4505.2650985858845</v>
-      </c>
-      <c r="V29" s="21">
+        <v>4505.2650985858827</v>
+      </c>
+      <c r="V29" s="20">
         <v>5044.79057984681</v>
       </c>
-      <c r="X29" s="17" t="str">
+      <c r="X29" s="16" t="str">
         <v>amazon google 1.00 1.00</v>
       </c>
-      <c r="Y29" s="18">
-        <v>4511.8491698768121</v>
-      </c>
-      <c r="Z29" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y29" s="17">
+        <v>4511.849169876813</v>
+      </c>
+      <c r="Z29" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.45">
       <c r="C30" t="e">
         <v>#N/A</v>
       </c>
@@ -3057,22 +3050,22 @@
         <v>amazon amazon 1.00 1.00</v>
       </c>
       <c r="U30" s="7">
-        <v>9427.265093697164</v>
-      </c>
-      <c r="V30" s="21">
+        <v>9427.2650936971622</v>
+      </c>
+      <c r="V30" s="20">
         <v>10225.23606062171</v>
       </c>
-      <c r="X30" s="17" t="str">
+      <c r="X30" s="16" t="str">
         <v>amazon amazon 1.00 1.00</v>
       </c>
-      <c r="Y30" s="18">
-        <v>9426.5431887968825</v>
-      </c>
-      <c r="Z30" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Y30" s="17">
+        <v>9426.5431887968844</v>
+      </c>
+      <c r="Z30" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="S31" s="7">
@@ -3084,20 +3077,20 @@
       <c r="U31" s="7">
         <v>1064.5798956631425</v>
       </c>
-      <c r="V31" s="21">
+      <c r="V31" s="20">
         <v>1256.3880030913922</v>
       </c>
-      <c r="X31" s="17" t="str">
+      <c r="X31" s="16" t="str">
         <v>starbucks google 1.00 1.00</v>
       </c>
-      <c r="Y31" s="18">
+      <c r="Y31" s="17">
         <v>1065.7647819045646</v>
       </c>
-      <c r="Z31" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.4">
+      <c r="Z31" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>19</v>
       </c>
@@ -3132,20 +3125,20 @@
       <c r="U32" s="7">
         <v>2168.798536799241</v>
       </c>
-      <c r="V32" s="21">
+      <c r="V32" s="20">
         <v>2490.6275448812899</v>
       </c>
-      <c r="X32" s="17" t="str">
+      <c r="X32" s="16" t="str">
         <v>starbucks amazon 1.00 1.00</v>
       </c>
-      <c r="Y32" s="18">
-        <v>2168.8987778657665</v>
-      </c>
-      <c r="Z32" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="Y32" s="17">
+        <v>2168.898777865767</v>
+      </c>
+      <c r="Z32" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B33">
         <f t="array" ref="B33:B35">TRANSPOSE(D8:F8)</f>
         <v>50</v>
@@ -3160,19 +3153,19 @@
       </c>
       <c r="E33" s="7">
         <f>IF(F19=0,E19/D33,E19)</f>
-        <v>66.666666666666671</v>
-      </c>
-      <c r="F33" s="11">
+        <v>66.666666666666657</v>
+      </c>
+      <c r="F33" s="7">
         <f>IF(D19="subnormal",E33-B33,E33+B33)</f>
-        <v>16.666666666666671</v>
+        <v>16.666666666666657</v>
       </c>
       <c r="G33" s="7">
         <f>F33^2*(EXP(D33^2)-1)</f>
-        <v>120.36928182231684</v>
+        <v>120.36928182231664</v>
       </c>
       <c r="H33" s="7">
         <f>SQRT(G33)</f>
-        <v>10.971293534598226</v>
+        <v>10.971293534598217</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -3185,20 +3178,20 @@
       <c r="U33" s="7">
         <v>602.83449581503703</v>
       </c>
-      <c r="V33" s="21">
+      <c r="V33" s="20">
         <v>677.36004466031011</v>
       </c>
-      <c r="X33" s="17" t="str">
+      <c r="X33" s="16" t="str">
         <v>starbucks starbucks 1.00 1.00</v>
       </c>
-      <c r="Y33" s="18">
-        <v>601.36234481090435</v>
-      </c>
-      <c r="Z33" s="17" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.4">
+      <c r="Y33" s="17">
+        <v>601.36234481090446</v>
+      </c>
+      <c r="Z33" s="16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>100</v>
       </c>
@@ -3214,7 +3207,7 @@
         <f>IF(F20=0,E20/D34,E20)</f>
         <v>200.00000000000006</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="7">
         <f>IF(D20="subnormal",E34-B34,E34+B34)</f>
         <v>300.00000000000006</v>
       </c>
@@ -3249,29 +3242,29 @@
       </c>
       <c r="P34" s="10">
         <f>N34*F33*F34*(EXP(N34*L34*D33*D34*K32)-1)</f>
-        <v>22.449450852147237</v>
+        <v>22.449450852147216</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R34" s="10">
         <f>W72</f>
-        <v>21.774727170018195</v>
-      </c>
-      <c r="S34" s="19">
+        <v>21.774727170015467</v>
+      </c>
+      <c r="S34" s="18">
         <v>-3.9997573158002782</v>
       </c>
       <c r="T34" t="str">
         <v>google 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U34" s="19">
-        <v>-3.7880784844280515</v>
-      </c>
-      <c r="V34" s="21">
+      <c r="U34" s="18">
+        <v>-3.7880784844280528</v>
+      </c>
+      <c r="V34" s="20">
         <v>2.5508998007966419E-4</v>
       </c>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:26" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>25</v>
       </c>
@@ -3285,19 +3278,19 @@
       </c>
       <c r="E35" s="7">
         <f>IF(F21=0,E21/D35,E21)</f>
-        <v>33.333333333333329</v>
-      </c>
-      <c r="F35" s="11">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="F35" s="7">
         <f>IF(D21="subnormal",E35-B35,E35+B35)</f>
-        <v>8.3333333333333286</v>
+        <v>8.3333333333333357</v>
       </c>
       <c r="G35" s="7">
         <f t="shared" si="0"/>
-        <v>52.434351177798455</v>
+        <v>52.43435117779854</v>
       </c>
       <c r="H35" s="7">
         <f>SQRT(G35)</f>
-        <v>7.241156756886185</v>
+        <v>7.2411567568861912</v>
       </c>
       <c r="J35" s="6" t="str">
         <f>C34&amp;"/"&amp;C35</f>
@@ -3322,29 +3315,29 @@
       </c>
       <c r="P35" s="10">
         <f>N35*F34*F35*(EXP(N35*L35*D34*D35*K32)-1)</f>
-        <v>-4.6918972791198925</v>
+        <v>-4.691897279119897</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>29</v>
       </c>
       <c r="R35" s="10">
         <f>Y72</f>
-        <v>-5.947162173990364</v>
-      </c>
-      <c r="S35" s="19">
+        <v>-5.9471621739908187</v>
+      </c>
+      <c r="S35" s="18">
         <v>-1.1740332356118037E-4</v>
       </c>
       <c r="T35" t="str">
         <v>amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U35" s="19">
-        <v>0.4784583559430402</v>
-      </c>
-      <c r="V35" s="21">
+      <c r="U35" s="18">
+        <v>0.47845835594303904</v>
+      </c>
+      <c r="V35" s="20">
         <v>-1.1939321040121053E-4</v>
       </c>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J36" s="6" t="s">
         <v>26</v>
       </c>
@@ -3374,22 +3367,22 @@
       </c>
       <c r="R36" s="10">
         <f>W73</f>
-        <v>4.0007883135083375</v>
-      </c>
-      <c r="S36" s="19">
+        <v>4.0007883135081101</v>
+      </c>
+      <c r="S36" s="18">
         <v>4.2800622399665036E-4</v>
       </c>
       <c r="T36" t="str">
         <v>starbucks 0.50 0.50 - 1.00 1.00</v>
       </c>
-      <c r="U36" s="19">
-        <v>0.11377110942236469</v>
-      </c>
-      <c r="V36" s="21">
+      <c r="U36" s="18">
+        <v>0.11377110942236501</v>
+      </c>
+      <c r="V36" s="20">
         <v>3.2923555692051073E-4</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="S37" s="7">
@@ -3399,21 +3392,21 @@
         <v>google google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U37" s="7">
-        <v>104.05245292089364</v>
-      </c>
-      <c r="V37" s="21">
+        <v>104.05245292089357</v>
+      </c>
+      <c r="V37" s="20">
         <v>65.517046672380232</v>
       </c>
       <c r="W37" s="7">
         <f t="array" ref="W37:W42">W19:W24</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="Y37" s="10">
         <f>U37-U34*U34</f>
-        <v>89.702914316706924</v>
-      </c>
-    </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.4">
+        <v>89.702914316706838</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="S38" s="7">
@@ -3423,16 +3416,16 @@
         <v>amazon google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U38" s="7">
-        <v>24.925026370739346</v>
-      </c>
-      <c r="V38" s="21">
+        <v>24.925026370739303</v>
+      </c>
+      <c r="V38" s="20">
         <v>22.337743324818906</v>
       </c>
       <c r="W38" s="7">
-        <v>21.774727170018195</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.4">
+        <v>21.774727170015467</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -3449,16 +3442,16 @@
         <v>amazon amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U39" s="7">
-        <v>109.92012331853519</v>
-      </c>
-      <c r="V39" s="21">
+        <v>109.92012331853532</v>
+      </c>
+      <c r="V39" s="20">
         <v>112.70654695394161</v>
       </c>
       <c r="W39" s="7">
-        <v>109.19713309243889</v>
-      </c>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.4">
+        <v>109.19713309243161</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -3475,16 +3468,16 @@
         <v>starbucks google 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U40" s="7">
-        <v>4.5089139598671686</v>
-      </c>
-      <c r="V40" s="21">
+        <v>4.5089139598671659</v>
+      </c>
+      <c r="V40" s="20">
         <v>3.2172061836399646</v>
       </c>
       <c r="W40" s="7">
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.4">
+        <v>4.0007883135081101</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -3501,16 +3494,16 @@
         <v>starbucks amazon 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U41" s="7">
-        <v>-5.8557281459403576</v>
-      </c>
-      <c r="V41" s="21">
+        <v>-5.8557281459403585</v>
+      </c>
+      <c r="V41" s="20">
         <v>-4.7062732320813385</v>
       </c>
       <c r="W41" s="7">
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.4">
+        <v>-5.9471621739908187</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -3527,16 +3520,16 @@
         <v>starbucks starbucks 0.50 0.50 - 1.00 1.00</v>
       </c>
       <c r="U42" s="7">
-        <v>48.695231506868787</v>
-      </c>
-      <c r="V42" s="21">
+        <v>48.695231506868858</v>
+      </c>
+      <c r="V42" s="20">
         <v>29.815772011327422</v>
       </c>
       <c r="W42" s="7">
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.4">
+        <v>37.317708459104438</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -3553,7 +3546,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -3570,7 +3563,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -3587,7 +3580,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -3604,7 +3597,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -3621,7 +3614,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -3638,7 +3631,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -3655,7 +3648,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -3672,7 +3665,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -3689,7 +3682,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -3700,7 +3693,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -3711,7 +3704,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -3722,7 +3715,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -3733,7 +3726,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -3747,7 +3740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -3763,10 +3756,10 @@
       </c>
       <c r="W57" s="9">
         <f>U16</f>
-        <v>50.250643505236695</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.4">
+        <v>50.250643505236702</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -3781,10 +3774,10 @@
       </c>
       <c r="W58" s="9">
         <f>U17</f>
-        <v>95.476143613249917</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.4">
+        <v>95.476143613249945</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -3802,7 +3795,7 @@
         <v>22.612857494939018</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -3813,7 +3806,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -3827,19 +3820,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.45">
       <c r="W62" s="7">
         <f t="array" ref="W62:Y62">TRANSPOSE(U64:U66)</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X62" s="7">
-        <v>95.476143613249917</v>
+        <v>95.476143613249945</v>
       </c>
       <c r="Y62" s="7">
         <v>22.612857494939018</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.45">
       <c r="W63" t="str">
         <f t="array" ref="W63:Y63">TRANSPOSE(V64:V66)</f>
         <v>google</v>
@@ -3851,10 +3844,10 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:25" x14ac:dyDescent="0.45">
       <c r="U64" s="7">
         <f t="array" ref="U64:U66">W57:W59</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V64" t="str">
         <f t="array" ref="V64:V66">V57:V59</f>
@@ -3873,9 +3866,9 @@
         <v>1140.3114289264086</v>
       </c>
     </row>
-    <row r="65" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="65" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U65" s="7">
-        <v>95.476143613249917</v>
+        <v>95.476143613249945</v>
       </c>
       <c r="V65" t="str">
         <v>amazon</v>
@@ -3886,14 +3879,14 @@
       </c>
       <c r="X65" s="9">
         <f>U21</f>
-        <v>9224.8911323503617</v>
+        <v>9224.8911323503598</v>
       </c>
       <c r="Y65" s="9">
         <f>X66</f>
         <v>2153.0412675187622</v>
       </c>
     </row>
-    <row r="66" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="66" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U66" s="7">
         <v>22.612857494939018</v>
       </c>
@@ -3910,27 +3903,27 @@
       </c>
       <c r="Y66" s="9">
         <f>U24</f>
-        <v>548.65903254552404</v>
-      </c>
-    </row>
-    <row r="68" spans="20:25" x14ac:dyDescent="0.4">
+        <v>548.65903254552416</v>
+      </c>
+    </row>
+    <row r="68" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W68" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="69" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W69" s="7">
         <f t="array" ref="W69:Y69">W62:Y62</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="X69" s="7">
-        <v>95.476143613249917</v>
+        <v>95.476143613249945</v>
       </c>
       <c r="Y69" s="7">
         <v>22.612857494939018</v>
       </c>
     </row>
-    <row r="70" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="70" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W70" t="str">
         <f t="array" ref="W70:Y70">TRANSPOSE(V71:V73)</f>
         <v>google</v>
@@ -3942,10 +3935,10 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="71" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="71" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U71" s="7">
         <f t="array" ref="U71:U73">U64:U66</f>
-        <v>50.250643505236695</v>
+        <v>50.250643505236702</v>
       </c>
       <c r="V71" t="str">
         <f t="array" ref="V71:V73">V64:V66</f>
@@ -3953,38 +3946,38 @@
       </c>
       <c r="W71" s="9">
         <f t="shared" ref="W71:Y73" si="1">W64-$U71*W$69</f>
-        <v>53.139006281224283</v>
+        <v>53.139006281223828</v>
       </c>
       <c r="X71" s="9">
         <f t="shared" si="1"/>
-        <v>21.774727170018195</v>
+        <v>21.774727170015467</v>
       </c>
       <c r="Y71" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
-      </c>
-    </row>
-    <row r="72" spans="20:25" x14ac:dyDescent="0.4">
+        <v>4.0007883135081101</v>
+      </c>
+    </row>
+    <row r="72" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U72" s="7">
-        <v>95.476143613249917</v>
+        <v>95.476143613249945</v>
       </c>
       <c r="V72" t="str">
         <v>amazon</v>
       </c>
       <c r="W72" s="9">
         <f t="shared" si="1"/>
-        <v>21.774727170018195</v>
+        <v>21.774727170015467</v>
       </c>
       <c r="X72" s="9">
         <f t="shared" si="1"/>
-        <v>109.19713309243889</v>
+        <v>109.19713309243161</v>
       </c>
       <c r="Y72" s="9">
         <f t="shared" si="1"/>
-        <v>-5.947162173990364</v>
-      </c>
-    </row>
-    <row r="73" spans="20:25" x14ac:dyDescent="0.4">
+        <v>-5.9471621739908187</v>
+      </c>
+    </row>
+    <row r="73" spans="20:25" x14ac:dyDescent="0.45">
       <c r="U73" s="7">
         <v>22.612857494939018</v>
       </c>
@@ -3993,37 +3986,37 @@
       </c>
       <c r="W73" s="9">
         <f t="shared" si="1"/>
-        <v>4.0007883135083375</v>
+        <v>4.0007883135081101</v>
       </c>
       <c r="X73" s="9">
         <f t="shared" si="1"/>
-        <v>-5.947162173990364</v>
+        <v>-5.9471621739908187</v>
       </c>
       <c r="Y73" s="9">
         <f t="shared" si="1"/>
-        <v>37.317708459104324</v>
-      </c>
-    </row>
-    <row r="75" spans="20:25" x14ac:dyDescent="0.4">
+        <v>37.317708459104438</v>
+      </c>
+    </row>
+    <row r="75" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W75" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="76" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W76" s="7">
         <f>SQRT(W71)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="X76" s="7">
         <f>SQRT(X72)</f>
-        <v>10.449743207009391</v>
+        <v>10.449743207009043</v>
       </c>
       <c r="Y76" s="7">
         <f>SQRT(Y73)</f>
-        <v>6.1088221826391642</v>
-      </c>
-    </row>
-    <row r="77" spans="20:25" x14ac:dyDescent="0.4">
+        <v>6.108822182639174</v>
+      </c>
+    </row>
+    <row r="77" spans="20:25" x14ac:dyDescent="0.45">
       <c r="W77" t="str">
         <f t="array" ref="W77:Y77">TRANSPOSE(V78:V80)</f>
         <v>google</v>
@@ -4035,14 +4028,14 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="78" spans="20:25" x14ac:dyDescent="0.4">
+    <row r="78" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T78" s="10">
         <f>U78/W57</f>
-        <v>0.14506581646941213</v>
+        <v>0.1450658164694115</v>
       </c>
       <c r="U78" s="7">
         <f t="array" ref="U78:U80">TRANSPOSE(W76:Y76)</f>
-        <v>7.2896506282005236</v>
+        <v>7.2896506282004925</v>
       </c>
       <c r="V78" t="str">
         <f t="array" ref="V78:V80">V71:V73</f>
@@ -4054,27 +4047,27 @@
       </c>
       <c r="X78" s="9">
         <f t="shared" si="2"/>
-        <v>0.28585144347144498</v>
+        <v>0.28585144347141994</v>
       </c>
       <c r="Y78" s="9">
         <f t="shared" si="2"/>
-        <v>8.98424061952042E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="20:25" x14ac:dyDescent="0.4">
+        <v>8.9842406195199329E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T79" s="10">
         <f>U79/W58</f>
-        <v>0.10944873568981481</v>
+        <v>0.10944873568981113</v>
       </c>
       <c r="U79" s="7">
-        <v>10.449743207009391</v>
+        <v>10.449743207009043</v>
       </c>
       <c r="V79" t="str">
         <v>amazon</v>
       </c>
       <c r="W79" s="9">
         <f t="shared" si="2"/>
-        <v>0.28585144347144503</v>
+        <v>0.28585144347141994</v>
       </c>
       <c r="X79" s="9">
         <f t="shared" si="2"/>
@@ -4082,31 +4075,31 @@
       </c>
       <c r="Y79" s="9">
         <f t="shared" si="2"/>
-        <v>-9.3163689561357926E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="20:25" x14ac:dyDescent="0.4">
+        <v>-9.3163689561368015E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="20:25" x14ac:dyDescent="0.45">
       <c r="T80" s="10">
         <f>U80/W59</f>
-        <v>0.27014817494898108</v>
+        <v>0.27014817494898152</v>
       </c>
       <c r="U80" s="7">
-        <v>6.1088221826391642</v>
+        <v>6.108822182639174</v>
       </c>
       <c r="V80" t="str">
         <v>starbucks</v>
       </c>
       <c r="W80" s="9">
         <f t="shared" si="2"/>
-        <v>8.9842406195204214E-2</v>
+        <v>8.9842406195199342E-2</v>
       </c>
       <c r="X80" s="9">
         <f t="shared" si="2"/>
-        <v>-9.3163689561357926E-2</v>
+        <v>-9.3163689561368002E-2</v>
       </c>
       <c r="Y80" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
   </sheetData>
@@ -4118,62 +4111,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C3:AA61"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.15234375" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.15234375" style="8"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="8"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.02</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -4190,75 +4183,75 @@
         <v>starbucks</v>
       </c>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>50</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>100</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>25</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>0</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -4274,8 +4267,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.3</v>
       </c>
       <c r="E12" s="2">
@@ -4286,18 +4279,18 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.1</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>-0.1</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -4308,7 +4301,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
@@ -4325,7 +4318,7 @@
       <c r="K16" s="6"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -4337,7 +4330,7 @@
       <c r="K17" s="6"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -4349,7 +4342,7 @@
       <c r="K18" s="6"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
@@ -4361,14 +4354,14 @@
       <c r="K19" s="6"/>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.45">
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
         <v>33</v>
       </c>
@@ -4378,7 +4371,7 @@
       <c r="K21" s="6"/>
       <c r="O21" s="9"/>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
         <v>34</v>
       </c>
@@ -4386,7 +4379,7 @@
       <c r="K22" s="6"/>
       <c r="O22" s="9"/>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C23" t="str">
         <f t="array" ref="C23:C25">TRANSPOSE(D4:F4)</f>
         <v>google</v>
@@ -4398,7 +4391,7 @@
       <c r="K23" s="6"/>
       <c r="O23" s="9"/>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C24" t="str">
         <v>amazon</v>
       </c>
@@ -4409,7 +4402,7 @@
       <c r="K24" s="6"/>
       <c r="O24" s="9"/>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C25" t="str">
         <v>starbucks</v>
       </c>
@@ -4419,11 +4412,11 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C27" s="4" t="str">
         <f>_xll.xPutBaskets(C23:C25,D23:D25,D30,D32:F32,"bkt")</f>
         <v>bkt</v>
@@ -4431,15 +4424,15 @@
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
         <v>35</v>
       </c>
@@ -4449,18 +4442,18 @@
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.45">
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="M31" t="s">
         <v>31</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="24">
         <f>E32*EXP(1.5%)</f>
         <v>101.51130646157189</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C32" t="s">
         <v>36</v>
       </c>
@@ -4468,7 +4461,7 @@
         <f>0.9*E32</f>
         <v>90</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="24">
         <f>E8</f>
         <v>100</v>
       </c>
@@ -4483,15 +4476,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="11"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="J33" s="6"/>
       <c r="K33" s="5"/>
       <c r="L33" s="8"/>
-      <c r="M33" s="24" t="e">
+      <c r="M33" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N33,,Q33*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4499,12 +4492,12 @@
         <f t="array" ref="N33:N35">TRANSPOSE(D32:F32)</f>
         <v>90</v>
       </c>
-      <c r="P33" s="22" t="str">
+      <c r="P33" s="21" t="str">
         <f t="array" ref="P33:W42">_xll.xValue(D16,C27,TRUE,,,500000,TRUE)</f>
         <v>basket strike 90.00</v>
       </c>
       <c r="Q33">
-        <v>12.962626451582683</v>
+        <v>12.962626451582681</v>
       </c>
       <c r="R33" t="e">
         <v>#N/A</v>
@@ -4532,13 +4525,13 @@
         <v>11.78353772595541</v>
       </c>
     </row>
-    <row r="34" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="11"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="L34" s="8"/>
-      <c r="M34" s="24" t="e">
+      <c r="M34" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N34,,Q34*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4577,15 +4570,15 @@
         <v>5.8600268386718684</v>
       </c>
     </row>
-    <row r="35" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:27" x14ac:dyDescent="0.45">
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="11"/>
+      <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="J35" s="6"/>
       <c r="K35" s="5"/>
       <c r="L35" s="8"/>
-      <c r="M35" s="24" t="e">
+      <c r="M35" s="23" t="e">
         <f ca="1">_xll.sBlackImplied($D$30,N35,,Q35*EXP(2%),$N$31)</f>
         <v>#NAME?</v>
       </c>
@@ -4596,7 +4589,7 @@
         <v>basket strike 110.00</v>
       </c>
       <c r="Q35">
-        <v>2.9024499984701597</v>
+        <v>2.9024499984701593</v>
       </c>
       <c r="R35" t="e">
         <v>#N/A</v>
@@ -4624,7 +4617,7 @@
         <v>2.4506311356786377</v>
       </c>
     </row>
-    <row r="36" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="8"/>
@@ -4654,7 +4647,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="37" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="P37" t="e">
@@ -4682,13 +4675,13 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="38" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:27" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="L38" t="s">
         <v>37</v>
       </c>
-      <c r="M38" s="23" t="e">
+      <c r="M38" s="22" t="e">
         <f ca="1">M34</f>
         <v>#NAME?</v>
       </c>
@@ -4717,7 +4710,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="39" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -4759,7 +4752,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="40" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4794,7 +4787,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -4829,7 +4822,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -4864,7 +4857,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="43" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -4875,7 +4868,7 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
     </row>
-    <row r="44" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -4886,7 +4879,7 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
     </row>
-    <row r="45" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -4897,7 +4890,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
     </row>
-    <row r="46" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -4908,7 +4901,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
     </row>
-    <row r="47" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -4919,7 +4912,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="3:27" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:27" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -4930,7 +4923,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -4941,7 +4934,7 @@
       <c r="J49" s="6"/>
       <c r="K49" s="6"/>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -4952,7 +4945,7 @@
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
     </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -4963,7 +4956,7 @@
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
     </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -4974,7 +4967,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4985,7 +4978,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
     </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4996,7 +4989,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -5007,7 +5000,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -5018,7 +5011,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -5029,7 +5022,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -5040,7 +5033,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -5051,7 +5044,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -5062,7 +5055,7 @@
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:11" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -5082,64 +5075,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="C3:Y104"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.15234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.15234375" style="8"/>
-    <col min="10" max="10" width="15.84375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.15234375" style="8"/>
-    <col min="13" max="13" width="37.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.69140625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="8"/>
+    <col min="10" max="10" width="15.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="8"/>
+    <col min="13" max="13" width="37.53125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.45">
       <c r="H3" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>0</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>0.01</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0.25</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -5156,76 +5149,76 @@
         <v>luckin</v>
       </c>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="H7" s="15">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="H7" s="14">
         <v>0.25</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <v>0</v>
       </c>
-      <c r="N7" s="24"/>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+      <c r="N7" s="23"/>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>43.71</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="11">
         <v>63.8</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <v>26.96</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.75</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0.45</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>0.5</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>-0.1</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>-0.5</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>-0.2</v>
       </c>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C11" t="s">
         <v>6</v>
       </c>
@@ -5233,38 +5226,38 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <f ca="1">D12</f>
+        <f>D12</f>
         <v>0.5</v>
       </c>
       <c r="F11">
-        <f ca="1">D13</f>
+        <f>D13</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D12" s="12">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D12" s="11">
         <v>0.5</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12">
-        <f ca="1">E13</f>
+        <f>E13</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="D13" s="12">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.45">
+      <c r="D13" s="11">
         <v>0.2</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="11">
         <v>0.2</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C15" s="3"/>
       <c r="D15" s="6"/>
       <c r="E15" s="4"/>
@@ -5275,12 +5268,12 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.45">
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="4" t="str">
-        <f ca="1">_xll.xPutDLM(D4:F4,D8:F8,D9:F9,D10:F10,D5,H4:J4,H7:H8,I7:K8,D11:F13,D6,"dlm")</f>
+        <f>_xll.xPutDLM(D4:F4,D8:F8,D9:F9,D10:F10,D5,H4:J4,H7:H8,I7:K8,D11:F13,D6,"dlm")</f>
         <v>dlm</v>
       </c>
       <c r="E16" s="4"/>
@@ -5291,7 +5284,7 @@
       <c r="K16" s="6"/>
       <c r="O16" s="9"/>
     </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -5303,7 +5296,7 @@
       <c r="K17" s="6"/>
       <c r="O17" s="9"/>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5315,17 +5308,17 @@
       <c r="K18" s="6"/>
       <c r="O18" s="9"/>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>43.71</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="11">
         <v>63.8</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <v>26.96</v>
       </c>
       <c r="G19" s="4"/>
@@ -5341,7 +5334,7 @@
       </c>
       <c r="O19" s="9"/>
     </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C20" t="s">
         <v>35</v>
       </c>
@@ -5360,7 +5353,7 @@
       </c>
       <c r="O20" s="9"/>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C21" t="s">
         <v>40</v>
       </c>
@@ -5373,11 +5366,11 @@
       <c r="K21" s="6"/>
       <c r="O21" s="9"/>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C22" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <v>1</v>
       </c>
       <c r="H22"/>
@@ -5385,11 +5378,11 @@
       <c r="J22"/>
       <c r="K22"/>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C23" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>0.76</v>
       </c>
       <c r="H23"/>
@@ -5397,11 +5390,11 @@
       <c r="J23"/>
       <c r="K23"/>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>0.36</v>
       </c>
       <c r="H24"/>
@@ -5409,7 +5402,7 @@
       <c r="J24"/>
       <c r="K24"/>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C25" t="s">
         <v>43</v>
       </c>
@@ -5421,11 +5414,11 @@
       <c r="J25"/>
       <c r="K25"/>
       <c r="N25" s="1">
-        <f ca="1">N27-N26</f>
+        <f>N27-N26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
@@ -5434,10 +5427,10 @@
         <v>0.96495976051676235</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C27" s="4"/>
       <c r="D27" t="str">
-        <f ca="1">_xll.xPutAutocall(D4:F4,D19:F19,D20,D21,D22,D23,D24,D25,"autocall")</f>
+        <f>_xll.xPutAutocall(D4:F4,D19:F19,D20,D21,D22,D23,D24,D25,"autocall")</f>
         <v>autocall</v>
       </c>
       <c r="H27"/>
@@ -5445,61 +5438,49 @@
       <c r="J27"/>
       <c r="K27"/>
       <c r="M27" s="4" t="str">
-        <f t="array" aca="1" ref="M27:Y46" ca="1">_xll.xValue(D16,D27,TRUE,,,N19,N20)</f>
+        <f t="array" ref="M27:Y46">_xll.xValue(D16,D27,TRUE,,,N19,N20)</f>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N27" s="6">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X27" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y27" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.45">
       <c r="D28" t="str">
-        <f ca="1">_xll.xPayoffIds(D27)</f>
+        <f>_xll.xPayoffIds(D27)</f>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="H28"/>
@@ -5507,635 +5488,492 @@
       <c r="J28"/>
       <c r="K28"/>
       <c r="M28" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N28" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X28" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y28" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
       <c r="M29" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N29" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X29" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y29" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
       <c r="M30" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N30" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X30" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y30" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="M31" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N31" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X31" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y31" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="M32" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N32" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X32" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y32" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
       <c r="M33" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N33" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X33" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y33" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
       <c r="M34" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N34" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X34" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y34" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
       <c r="M35" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N35" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X35" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y35" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.45">
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
       <c r="M36" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N36" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X36" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y36" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.45">
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="M37" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N37" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X37" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y37" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.45">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
-      <c r="M38" s="27" t="str">
-        <f ca="1"/>
+      <c r="M38" s="26" t="str">
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N38" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X38" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y38" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -6146,59 +5984,46 @@
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="M39" s="5" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N39" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X39" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y39" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="40" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -6209,59 +6034,46 @@
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="M40" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N40" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X40" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y40" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -6272,59 +6084,46 @@
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
       <c r="M41" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N41" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X41" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y41" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -6335,59 +6134,46 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="M42" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N42" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X42" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y42" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -6398,59 +6184,46 @@
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="M43" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N43" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X43" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y43" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -6461,59 +6234,46 @@
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
       <c r="M44" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N44" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X44" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y44" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -6524,59 +6284,46 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="M45" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N45" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X45" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y45" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -6587,59 +6334,46 @@
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="M46" s="4" t="str">
-        <f ca="1"/>
         <v>autocall strike 76 KO 100 CPN 36 6 periods of 1m</v>
       </c>
       <c r="N46" s="4">
-        <f ca="1"/>
-        <v>0.96495976051676235</v>
+        <v>0.96495976051676258</v>
       </c>
       <c r="O46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="P46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Q46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="R46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="S46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="T46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="U46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="V46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="W46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="X46" s="4" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="Y46" s="4" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -6650,7 +6384,7 @@
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
     </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.45">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -6661,15 +6395,14 @@
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="M48" s="4" t="str">
-        <f t="array" aca="1" ref="M48:N104" ca="1">_xll.xAADrisk(D16,D27,D28,TRUE,,,N19,N20)</f>
+        <f t="array" ref="M48:N104">_xll.xAADrisk(D16,D27,D28,TRUE,,,N19,N20)</f>
         <v>value</v>
       </c>
       <c r="N48" s="8">
-        <f ca="1"/>
-        <v>0.96495976051676247</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.4">
+        <v>0.96495976051676258</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -6683,15 +6416,13 @@
         <v>0</v>
       </c>
       <c r="M49" t="str">
-        <f ca="1"/>
         <v>disc rate</v>
       </c>
-      <c r="N49" s="24">
-        <f ca="1"/>
-        <v>-0.1147608559187607</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N49" s="23">
+        <v>-0.11476085591875966</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -6705,15 +6436,13 @@
         <v>1</v>
       </c>
       <c r="M50" t="str">
-        <f ca="1"/>
         <v>spot uber</v>
       </c>
       <c r="N50" s="8">
-        <f ca="1"/>
-        <v>8.4753531785410605E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.4">
+        <v>8.4753531785410627E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -6727,15 +6456,13 @@
         <v>2</v>
       </c>
       <c r="M51" t="str">
-        <f ca="1"/>
         <v>spot lyft</v>
       </c>
-      <c r="N51" s="31">
-        <f ca="1"/>
-        <v>8.2817410998347761E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N51" s="30">
+        <v>8.2817410998347566E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -6749,15 +6476,13 @@
         <v>3</v>
       </c>
       <c r="M52" t="str">
-        <f ca="1"/>
         <v>spot luckin</v>
       </c>
       <c r="N52" s="8">
-        <f ca="1"/>
         <v>4.3564639889824208E-3</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -6771,15 +6496,13 @@
         <v>4</v>
       </c>
       <c r="M53" t="str">
-        <f ca="1"/>
         <v>repo spread uber</v>
       </c>
-      <c r="N53" s="24">
-        <f ca="1"/>
-        <v>-2.858083270914898E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N53" s="23">
+        <v>-2.8580832709148987E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -6793,15 +6516,13 @@
         <v>5</v>
       </c>
       <c r="M54" t="str">
-        <f ca="1"/>
         <v>repo spread lyft</v>
       </c>
-      <c r="N54" s="24">
-        <f ca="1"/>
-        <v>-7.0428767478183302E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N54" s="23">
+        <v>-7.0428767478183329E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -6815,15 +6536,13 @@
         <v>6</v>
       </c>
       <c r="M55" t="str">
-        <f ca="1"/>
         <v>repo spread luckin</v>
       </c>
-      <c r="N55" s="24">
-        <f ca="1"/>
+      <c r="N55" s="23">
         <v>-7.9014360190003866E-2</v>
       </c>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -6837,15 +6556,13 @@
         <v>7</v>
       </c>
       <c r="M56" t="str">
-        <f ca="1"/>
         <v>div uber 0.25</v>
       </c>
-      <c r="N56" s="24">
-        <f ca="1"/>
-        <v>-5.89291818494658E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N56" s="23">
+        <v>-5.892918184946578E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -6859,15 +6576,13 @@
         <v>8</v>
       </c>
       <c r="M57" t="str">
-        <f ca="1"/>
         <v>div lyft 0.25</v>
       </c>
-      <c r="N57" s="24">
-        <f ca="1"/>
-        <v>-0.11769615504528579</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N57" s="23">
+        <v>-0.11769615504528574</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -6881,15 +6596,13 @@
         <v>9</v>
       </c>
       <c r="M58" t="str">
-        <f ca="1"/>
         <v>div luckin 0.25</v>
       </c>
-      <c r="N58" s="24">
-        <f ca="1"/>
+      <c r="N58" s="23">
         <v>-0.14837682083622522</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -6903,15 +6616,13 @@
         <v>10</v>
       </c>
       <c r="M59" t="str">
-        <f ca="1"/>
         <v>div uber 0.75</v>
       </c>
-      <c r="N59" s="24">
-        <f ca="1"/>
+      <c r="N59" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -6925,15 +6636,13 @@
         <v>11</v>
       </c>
       <c r="M60" t="str">
-        <f ca="1"/>
         <v>div lyft 0.75</v>
       </c>
-      <c r="N60" s="24">
-        <f ca="1"/>
+      <c r="N60" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.45">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -6947,471 +6656,383 @@
         <v>12</v>
       </c>
       <c r="M61" t="str">
-        <f ca="1"/>
         <v>div luckin 0.75</v>
       </c>
-      <c r="N61" s="24">
-        <f ca="1"/>
+      <c r="N61" s="23">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.45">
       <c r="L62">
         <v>13</v>
       </c>
       <c r="M62" t="str">
-        <f ca="1"/>
         <v>ATM uber</v>
       </c>
-      <c r="N62" s="24">
-        <f ca="1"/>
-        <v>-7.2689795180755912E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.4">
-      <c r="L63" s="28">
+      <c r="N62" s="23">
+        <v>-7.2689795180755759E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="L63" s="27">
         <v>14</v>
       </c>
-      <c r="M63" s="28" t="str">
-        <f ca="1"/>
+      <c r="M63" s="27" t="str">
         <v>ATM lyft</v>
       </c>
-      <c r="N63" s="29">
-        <f ca="1"/>
-        <v>-0.15504777779332335</v>
-      </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.4">
+      <c r="N63" s="28">
+        <v>-0.15504777779332354</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.45">
       <c r="L64">
         <v>15</v>
       </c>
       <c r="M64" t="str">
-        <f ca="1"/>
         <v>ATM luckin</v>
       </c>
-      <c r="N64" s="24">
-        <f ca="1"/>
-        <v>-0.16802184695029357</v>
-      </c>
-    </row>
-    <row r="65" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N64" s="23">
+        <v>-0.16802184695029343</v>
+      </c>
+    </row>
+    <row r="65" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L65">
         <v>16</v>
       </c>
       <c r="M65" t="str">
-        <f ca="1"/>
         <v>skew uber</v>
       </c>
-      <c r="N65" s="26">
-        <f ca="1"/>
-        <v>2.6636703664252876E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="12:14" x14ac:dyDescent="0.4">
-      <c r="L66" s="28">
+      <c r="N65" s="25">
+        <v>2.6636703664253521E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="12:14" x14ac:dyDescent="0.45">
+      <c r="L66" s="27">
         <v>17</v>
       </c>
-      <c r="M66" s="28" t="str">
-        <f ca="1"/>
+      <c r="M66" s="27" t="str">
         <v>skew lyft</v>
       </c>
-      <c r="N66" s="30">
-        <f ca="1"/>
-        <v>5.9137145144274379E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N66" s="29">
+        <v>5.9137145144274164E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L67">
         <v>18</v>
       </c>
       <c r="M67" t="str">
-        <f ca="1"/>
         <v>skew luckin</v>
       </c>
-      <c r="N67" s="24">
-        <f ca="1"/>
-        <v>7.4092312588810466E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N67" s="23">
+        <v>7.4092312588810841E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L68">
         <v>19</v>
       </c>
       <c r="M68" t="str">
-        <f ca="1"/>
         <v>correl lyft uber</v>
       </c>
-      <c r="N68" s="24">
-        <f ca="1"/>
-        <v>8.2534884478533584E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N68" s="23">
+        <v>8.253488447853374E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L69">
         <v>20</v>
       </c>
       <c r="M69" t="str">
-        <f ca="1"/>
         <v>correl luckin uber</v>
       </c>
-      <c r="N69" s="24">
-        <f ca="1"/>
-        <v>6.0410904294307347E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N69" s="23">
+        <v>6.0410904294307503E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L70">
         <v>21</v>
       </c>
       <c r="M70" t="str">
-        <f ca="1"/>
         <v>correl luckin lyft</v>
       </c>
-      <c r="N70" s="24">
-        <f ca="1"/>
-        <v>1.7588752186493046E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N70" s="23">
+        <v>1.7588752186493042E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="12:14" x14ac:dyDescent="0.45">
       <c r="L71">
         <v>22</v>
       </c>
       <c r="M71" t="str">
-        <f ca="1"/>
         <v>lambda</v>
       </c>
-      <c r="N71" s="24">
-        <f ca="1"/>
-        <v>3.0707491088887599E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="12:14" x14ac:dyDescent="0.4">
+      <c r="N71" s="23">
+        <v>3.0707491088887633E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M72" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N72" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="73" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M73" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N73" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="74" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M74" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N74" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="75" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M75" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N75" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="76" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="76" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M76" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N76" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="77" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M77" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N77" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="78" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M78" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N78" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="79" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M79" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N79" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="80" spans="12:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="12:14" x14ac:dyDescent="0.45">
       <c r="M80" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N80" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="81" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M81" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N81" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M82" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N82" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="83" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M83" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N83" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M84" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N84" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="85" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M85" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N85" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="86" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M86" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N86" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="87" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M87" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N87" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="88" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M88" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N88" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="89" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M89" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N89" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="90" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M90" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N90" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="91" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M91" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N91" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="92" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M92" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N92" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="93" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M93" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N93" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="94" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M94" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N94" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="95" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="95" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M95" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N95" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="96" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="96" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M96" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N96" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="97" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M97" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N97" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="98" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M98" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N98" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="99" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M99" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N99" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="100" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M100" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N100" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="101" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M101" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N101" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="102" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="102" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M102" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N102" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="103" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="103" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M103" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N103" t="e">
-        <f ca="1"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="104" spans="13:14" x14ac:dyDescent="0.4">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="104" spans="13:14" x14ac:dyDescent="0.45">
       <c r="M104" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="N104" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -7419,13 +7040,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/testDLM.xlsx
+++ b/testDLM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bernardo\dev\my_repos\CompFinance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFCE1F1-2E9E-4BE8-A392-78740350B748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DC78A1-D274-4D92-9BA3-DB0DF8B5BD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27634" yWindow="926" windowWidth="24685" windowHeight="13114" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6439,7 +6439,7 @@
         <v>spot uber</v>
       </c>
       <c r="N50" s="8">
-        <v>8.4753531785410627E-4</v>
+        <v>8.475353178541066E-4</v>
       </c>
     </row>
     <row r="51" spans="3:14" x14ac:dyDescent="0.45">
@@ -6459,7 +6459,7 @@
         <v>spot lyft</v>
       </c>
       <c r="N51" s="30">
-        <v>8.2817410998347566E-4</v>
+        <v>8.2817410998347479E-4</v>
       </c>
     </row>
     <row r="52" spans="3:14" x14ac:dyDescent="0.45">
@@ -6479,7 +6479,7 @@
         <v>spot luckin</v>
       </c>
       <c r="N52" s="8">
-        <v>4.3564639889824208E-3</v>
+        <v>4.3564639889824277E-3</v>
       </c>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.45">
@@ -6519,7 +6519,7 @@
         <v>repo spread lyft</v>
       </c>
       <c r="N54" s="23">
-        <v>-7.0428767478183329E-2</v>
+        <v>-7.0428767478183302E-2</v>
       </c>
     </row>
     <row r="55" spans="3:14" x14ac:dyDescent="0.45">
@@ -6539,7 +6539,7 @@
         <v>repo spread luckin</v>
       </c>
       <c r="N55" s="23">
-        <v>-7.9014360190003866E-2</v>
+        <v>-7.9014360190003879E-2</v>
       </c>
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.45">
@@ -6559,7 +6559,7 @@
         <v>div uber 0.25</v>
       </c>
       <c r="N56" s="23">
-        <v>-5.892918184946578E-2</v>
+        <v>-5.89291818494658E-2</v>
       </c>
     </row>
     <row r="57" spans="3:14" x14ac:dyDescent="0.45">
@@ -6599,7 +6599,7 @@
         <v>div luckin 0.25</v>
       </c>
       <c r="N58" s="23">
-        <v>-0.14837682083622522</v>
+        <v>-0.14837682083622528</v>
       </c>
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.45">
@@ -6670,7 +6670,7 @@
         <v>ATM uber</v>
       </c>
       <c r="N62" s="23">
-        <v>-7.2689795180755759E-2</v>
+        <v>-7.2689795180755787E-2</v>
       </c>
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.45">
@@ -6681,7 +6681,7 @@
         <v>ATM lyft</v>
       </c>
       <c r="N63" s="28">
-        <v>-0.15504777779332354</v>
+        <v>-0.15504777779332365</v>
       </c>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.45">
@@ -6692,7 +6692,7 @@
         <v>ATM luckin</v>
       </c>
       <c r="N64" s="23">
-        <v>-0.16802184695029343</v>
+        <v>-0.16802184695029396</v>
       </c>
     </row>
     <row r="65" spans="12:14" x14ac:dyDescent="0.45">
@@ -6703,7 +6703,7 @@
         <v>skew uber</v>
       </c>
       <c r="N65" s="25">
-        <v>2.6636703664253521E-2</v>
+        <v>2.6636703664253428E-2</v>
       </c>
     </row>
     <row r="66" spans="12:14" x14ac:dyDescent="0.45">
@@ -6714,7 +6714,7 @@
         <v>skew lyft</v>
       </c>
       <c r="N66" s="29">
-        <v>5.9137145144274164E-2</v>
+        <v>5.9137145144274053E-2</v>
       </c>
     </row>
     <row r="67" spans="12:14" x14ac:dyDescent="0.45">
@@ -6725,7 +6725,7 @@
         <v>skew luckin</v>
       </c>
       <c r="N67" s="23">
-        <v>7.4092312588810841E-2</v>
+        <v>7.4092312588809106E-2</v>
       </c>
     </row>
     <row r="68" spans="12:14" x14ac:dyDescent="0.45">
@@ -6736,7 +6736,7 @@
         <v>correl lyft uber</v>
       </c>
       <c r="N68" s="23">
-        <v>8.253488447853374E-3</v>
+        <v>8.2534884478533601E-3</v>
       </c>
     </row>
     <row r="69" spans="12:14" x14ac:dyDescent="0.45">
@@ -6747,7 +6747,7 @@
         <v>correl luckin uber</v>
       </c>
       <c r="N69" s="23">
-        <v>6.0410904294307503E-3</v>
+        <v>6.0410904294307304E-3</v>
       </c>
     </row>
     <row r="70" spans="12:14" x14ac:dyDescent="0.45">
@@ -6758,7 +6758,7 @@
         <v>correl luckin lyft</v>
       </c>
       <c r="N70" s="23">
-        <v>1.7588752186493042E-2</v>
+        <v>1.7588752186493046E-2</v>
       </c>
     </row>
     <row r="71" spans="12:14" x14ac:dyDescent="0.45">
@@ -6769,7 +6769,7 @@
         <v>lambda</v>
       </c>
       <c r="N71" s="23">
-        <v>3.0707491088887633E-2</v>
+        <v>3.0707491088887606E-2</v>
       </c>
     </row>
     <row r="72" spans="12:14" x14ac:dyDescent="0.45">
